--- a/data/import/fabric/fabric.xlsx
+++ b/data/import/fabric/fabric.xlsx
@@ -2126,8 +2126,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2165,6 +2165,11 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2174,7 +2179,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2182,11 +2187,12 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2200,6 +2206,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2207,11 +2216,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns2:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns3:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2502,9 +2511,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
+  <cols xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <col min="1" max="1" width="37" customWidth="1"/>
     <col min="3" max="3" width="25.6640625" customWidth="1"/>
     <col min="4" max="4" width="17.83203125" customWidth="1"/>
@@ -2515,9 +2524,13 @@
     <col min="9" max="9" width="38.5" customWidth="1"/>
     <col min="10" max="10" width="21.83203125" customWidth="1"/>
     <col min="11" max="11" width="44.1640625" customWidth="1"/>
+    <col min="13" max="13" width="58" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="95" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="78" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="95" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2554,8 +2567,20 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="135" customHeight="1">
+      <c r="M1" s="0" t="str">
+        <v>name_zh</v>
+      </c>
+      <c r="N1" s="0" t="str">
+        <v>summary_zh</v>
+      </c>
+      <c r="O1" s="0" t="str">
+        <v>seo_title_zh</v>
+      </c>
+      <c r="P1" s="0" t="str">
+        <v>seo_description_zh</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="2" spans="1:15" ht="135" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -2590,11 +2615,20 @@
         <v>22</v>
       </c>
       <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-    </row>
-    <row r="3" spans="1:15" ht="60" customHeight="1">
+      <c r="M2" s="5" t="str">
+        <v>BMW 宝马方格复刻面料</v>
+      </c>
+      <c r="N2" s="5" t="str">
+        <v>适用于 BMW 宝马 Isetta 内饰的经典苏格兰方格面料。</v>
+      </c>
+      <c r="O2" s="5" t="str">
+        <v>BMW 宝马方格复刻面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P2" s="5" t="str">
+        <v>BMW 宝马方格复刻面料，经典苏格兰方格，适用于宝马 Isetta 内饰修复选材。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="3" spans="1:15" ht="60" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -2629,11 +2663,20 @@
         <v>32</v>
       </c>
       <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-    </row>
-    <row r="4" spans="1:15" ht="165" customHeight="1">
+      <c r="M3" s="5" t="str">
+        <v>BMW 宝马 M 条纹复刻面料</v>
+      </c>
+      <c r="N3" s="5" t="str">
+        <v>M-Stripe 座椅面料复刻了 BMW 宝马 M8 原型车所使用的经典 M 条纹材料。</v>
+      </c>
+      <c r="O3" s="5" t="str">
+        <v>BMW 宝马 M 条纹复刻面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P3" s="5" t="str">
+        <v>BMW 宝马 M 条纹复刻面料，M8 原型车风格的 M 条纹复刻座椅面料。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="4" spans="1:15" ht="165" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
@@ -2668,11 +2711,20 @@
         <v>42</v>
       </c>
       <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="1:15" ht="75" customHeight="1">
+      <c r="M4" s="5" t="str">
+        <v>千鸟格复合格纹汽车面料</v>
+      </c>
+      <c r="N4" s="5" t="str">
+        <v>以千鸟格为基础的格伦格纹融合苏格兰方格，形成细致的复合图案，适用于座椅软包。</v>
+      </c>
+      <c r="O4" s="5" t="str">
+        <v>千鸟格复合格纹汽车面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P4" s="5" t="str">
+        <v>千鸟格复合格纹汽车面料，千鸟格、格伦格纹与苏格兰方格组合，适用于汽车座椅软包。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="5" spans="1:15" ht="75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
@@ -2707,11 +2759,20 @@
         <v>52</v>
       </c>
       <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" ht="90" customHeight="1">
+      <c r="M5" s="5" t="str">
+        <v>Mercedes-Benz 奔驰方格复刻面料</v>
+      </c>
+      <c r="N5" s="5" t="str">
+        <v>参照第一代 Mercedes-Benz 奔驰 W460 G 级经典内饰规格与纹理制作的复刻面料。</v>
+      </c>
+      <c r="O5" s="5" t="str">
+        <v>Mercedes-Benz 奔驰方格复刻面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P5" s="5" t="str">
+        <v>Mercedes-Benz 奔驰方格复刻面料，适用于奔驰 W460 G 级经典内饰修复的方格复刻布料。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="6" spans="1:15" ht="90" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>53</v>
       </c>
@@ -2746,11 +2807,20 @@
         <v>62</v>
       </c>
       <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" ht="60" customHeight="1">
+      <c r="M6" s="5" t="str">
+        <v>Mercedes-Benz 奔驰 Rodeo 复刻面料</v>
+      </c>
+      <c r="N6" s="5" t="str">
+        <v>参照 20 世纪 80 年代末 Mercedes-Benz 奔驰 G 级原车内饰纹理制作的 Rodeo 复刻面料。相同图案也用于 2025 年 G550“Stronger Than the 1980s”特别版。</v>
+      </c>
+      <c r="O6" s="5" t="str">
+        <v>Mercedes-Benz 奔驰 Rodeo 复刻面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P6" s="5" t="str">
+        <v>Mercedes-Benz 奔驰 Rodeo 复刻面料，80 年代奔驰 G 级 Rodeo 风格复刻布料，适用于经典座舱修复。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="7" spans="1:15" ht="60" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,11 +2855,20 @@
         <v>72</v>
       </c>
       <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" ht="60" customHeight="1">
+      <c r="M7" s="5" t="str">
+        <v>Mercedes-Benz 奔驰纯羊毛格纹面料</v>
+      </c>
+      <c r="N7" s="5" t="str">
+        <v>采用 100% 纯羊毛织造，专为 Mercedes-Benz 奔驰 W198 300SL Gullwing 鸥翼车型的内饰修复选材设计。</v>
+      </c>
+      <c r="O7" s="5" t="str">
+        <v>Mercedes-Benz 奔驰纯羊毛格纹面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P7" s="5" t="str">
+        <v>Mercedes-Benz 奔驰纯羊毛格纹面料，100% 纯羊毛格纹，适用于奔驰 W198 300SL 鸥翼车型内饰修复。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="8" spans="1:15" ht="60" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>73</v>
       </c>
@@ -2824,11 +2903,20 @@
         <v>81</v>
       </c>
       <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" ht="60" customHeight="1">
+      <c r="M8" s="5" t="str">
+        <v>Porsche 保时捷方格复刻面料</v>
+      </c>
+      <c r="N8" s="5" t="str">
+        <v>适用于 Porsche 保时捷内饰软包的经典方格图案面料。</v>
+      </c>
+      <c r="O8" s="5" t="str">
+        <v>Porsche 保时捷方格复刻面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P8" s="5" t="str">
+        <v>Porsche 保时捷方格复刻面料，经典保时捷方格图案，适用于汽车内饰软包选材。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="9" spans="1:15" ht="60" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>82</v>
       </c>
@@ -2863,11 +2951,20 @@
         <v>91</v>
       </c>
       <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" ht="60" customHeight="1">
+      <c r="M9" s="5" t="str">
+        <v>Porsche 保时捷人字纹复刻面料</v>
+      </c>
+      <c r="N9" s="5" t="str">
+        <v>参照 Porsche 保时捷 924 原车座椅规格与纹理制作的人字纹汽车内饰复刻面料。</v>
+      </c>
+      <c r="O9" s="5" t="str">
+        <v>Porsche 保时捷人字纹复刻面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P9" s="5" t="str">
+        <v>Porsche 保时捷人字纹复刻面料，适用于保时捷 924 座椅修复的人字纹复刻布料。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="10" spans="1:15" ht="60" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>92</v>
       </c>
@@ -2902,11 +2999,20 @@
         <v>101</v>
       </c>
       <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" ht="60" customHeight="1">
+      <c r="M10" s="5" t="str">
+        <v>Porsche 保时捷 Madras 格纹面料</v>
+      </c>
+      <c r="N10" s="5" t="str">
+        <v>Madras 是 1972 至 1975 年间保时捷提供的经典内饰选装面料，曾用于早期 G-Model 911，包括 911T、911E、911S 及早期 Carrera 车型。</v>
+      </c>
+      <c r="O10" s="5" t="str">
+        <v>Porsche 保时捷 Madras 格纹面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P10" s="5" t="str">
+        <v>Porsche 保时捷 Madras 格纹面料，1972—1975 年保时捷 911 经典内饰风格，适用于 Madras 格纹修复选材。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="11" spans="1:15" ht="60" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>102</v>
       </c>
@@ -2941,11 +3047,20 @@
         <v>111</v>
       </c>
       <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" ht="60" customHeight="1">
+      <c r="M11" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料</v>
+      </c>
+      <c r="N11" s="5" t="str">
+        <v>Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。</v>
+      </c>
+      <c r="O11" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P11" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，经典 Pepita 千鸟格，适用于保时捷 356、911 内饰修复选材。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="12" spans="1:15" ht="60" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>112</v>
       </c>
@@ -2980,11 +3095,20 @@
         <v>121</v>
       </c>
       <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" ht="60" customHeight="1">
+      <c r="M12" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料</v>
+      </c>
+      <c r="N12" s="5" t="str">
+        <v>Pinstripe 以商务西装细条纹为灵感，是 20 世纪 70 年代末至 80 年代保时捷跑车内饰的代表性面料，曾广泛用于风冷 911 G-Model，以及前置发动机车型 924、944 和 928。</v>
+      </c>
+      <c r="O12" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P12" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料，经典西装式细条纹，适用于保时捷 911、924、944、928 内饰修复选材。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="13" spans="1:15" ht="60" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>122</v>
       </c>
@@ -3019,11 +3143,20 @@
         <v>126</v>
       </c>
       <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" ht="60" customHeight="1">
+      <c r="M13" s="5" t="str">
+        <v>Porsche 保时捷格纹复刻面料</v>
+      </c>
+      <c r="N13" s="5" t="str">
+        <v>为 1973 年 Porsche 保时捷 911 RSR 和 1975 年 914 车型复刻的平织格纹内饰面料。</v>
+      </c>
+      <c r="O13" s="5" t="str">
+        <v>Porsche 保时捷格纹复刻面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P13" s="5" t="str">
+        <v>Porsche 保时捷格纹复刻面料，1973 年 911 RSR 与 1975 年 914 风格格纹，材质以具体 SKU 规格为准。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="14" spans="1:15" ht="60" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>127</v>
       </c>
@@ -3058,11 +3191,20 @@
         <v>136</v>
       </c>
       <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" ht="60" customHeight="1">
+      <c r="M14" s="5" t="str">
+        <v>Porsche 保时捷绒面细条纹面料</v>
+      </c>
+      <c r="N14" s="5" t="str">
+        <v>密实的割绒表面带来近似天鹅绒的柔软、丰厚触感，是 20 世纪 80 年代豪华及商务风格跑车座舱中受到青睐的内饰面料。</v>
+      </c>
+      <c r="O14" s="5" t="str">
+        <v>Porsche 保时捷绒面细条纹面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P14" s="5" t="str">
+        <v>Porsche 保时捷绒面细条纹面料，密实割绒与细条纹，呈现 80 年代经典跑车座舱的柔软质感。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="15" spans="1:15" ht="60" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>137</v>
       </c>
@@ -3097,11 +3239,20 @@
         <v>146</v>
       </c>
       <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" ht="60" customHeight="1">
+      <c r="M15" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料</v>
+      </c>
+      <c r="N15" s="5" t="str">
+        <v>复刻保时捷标志性的 Studio Check 格纹，适用于 911 Carrera 的 964／993 代车型，以及 928、968 的内饰选材。</v>
+      </c>
+      <c r="O15" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P15" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料，Studio Check 格纹复刻，适用于保时捷 964、993、928、968 座舱修复。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="16" spans="1:15" ht="60" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>147</v>
       </c>
@@ -3136,11 +3287,20 @@
         <v>156</v>
       </c>
       <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" ht="60" customHeight="1">
+      <c r="M16" s="5" t="str">
+        <v>Porsche 保时捷苏格兰格纹面料</v>
+      </c>
+      <c r="N16" s="5" t="str">
+        <v>这一经典苏格兰格纹于 1975 年推出，曾是早期 Porsche 保时捷 911 Turbo（930）和 911SC 的知名内饰选装图案。</v>
+      </c>
+      <c r="O16" s="5" t="str">
+        <v>Porsche 保时捷苏格兰格纹面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P16" s="5" t="str">
+        <v>Porsche 保时捷苏格兰格纹面料，经典 Tartan 格纹，适用于保时捷 930 Turbo、911SC 座椅及门板修复选材。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="17" spans="1:15" ht="60" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>157</v>
       </c>
@@ -3175,11 +3335,20 @@
         <v>166</v>
       </c>
       <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="1:15" ht="60" customHeight="1">
+      <c r="M17" s="5" t="str">
+        <v>精选汽车座椅格纹面料</v>
+      </c>
+      <c r="N17" s="5" t="str">
+        <v>精选格纹面料，用于汽车座椅软包。</v>
+      </c>
+      <c r="O17" s="5" t="str">
+        <v>精选汽车座椅格纹面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P17" s="5" t="str">
+        <v>精选汽车座椅格纹面料，多款格纹可选，适用于汽车座椅软包与内饰选材。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="18" spans="1:15" ht="60" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>167</v>
       </c>
@@ -3214,11 +3383,20 @@
         <v>176</v>
       </c>
       <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" ht="70" customHeight="1">
+      <c r="M18" s="5" t="str">
+        <v>Spirit of Le Mans 勒芒风格羊毛格纹面料</v>
+      </c>
+      <c r="N18" s="5" t="str">
+        <v>Spirit of Le Mans（SOLM）羊毛系列以赛车运动为灵感，在苏格兰织造，专为高品质汽车内饰设计。采用 100% 羊毛与耐用的 2/2 斜纹组织，每延米重 500 克（365 克／平方米），并预先施加针对汽车安全要求的防污及阻燃处理。</v>
+      </c>
+      <c r="O18" s="5" t="str">
+        <v>Spirit of Le Mans 勒芒风格羊毛格纹面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P18" s="5" t="str">
+        <v>Spirit of Le Mans 勒芒风格羊毛格纹面料，苏格兰织造的 100% 羊毛赛车格纹，2/2 斜纹组织，带防污及阻燃预处理。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="19" spans="1:15" ht="70" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>177</v>
       </c>
@@ -3245,11 +3423,20 @@
         <v>182</v>
       </c>
       <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" ht="118" customHeight="1">
+      <c r="M19" s="5" t="str">
+        <v>BMW 宝马 ÜBERKARO 格纹复刻面料</v>
+      </c>
+      <c r="N19" s="5" t="str">
+        <v>BMW ÜBERKARO 是经典苏格兰格纹，因用于宝马 E30 及稀有的 M3 Evolution II 车型而闻名。</v>
+      </c>
+      <c r="O19" s="5" t="str">
+        <v>BMW 宝马 ÜBERKARO 格纹复刻面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P19" s="5" t="str">
+        <v>BMW 宝马 ÜBERKARO 格纹复刻面料，经典 ÜBERKARO 格纹，适用于宝马 E30、M3 Evolution II 内饰修复选材。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="20" spans="1:15" ht="118" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>183</v>
       </c>
@@ -3276,11 +3463,20 @@
         <v>188</v>
       </c>
       <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="1:15" ht="137" customHeight="1">
+      <c r="M20" s="5" t="str">
+        <v>BMW 宝马千鸟格复刻面料</v>
+      </c>
+      <c r="N20" s="5" t="str">
+        <v>德国复刻千鸟格（Pepita）座椅面料采用耐用的羊毛混纺结构，为经典 BMW 宝马 E10（2002）、E21、E28（5 系）及 E30（3 系，包括 325i 和早期 M3）提供接近原有风格的纹理与饰面，适合座椅中央拼片、门板和内饰修复。</v>
+      </c>
+      <c r="O20" s="5" t="str">
+        <v>BMW 宝马千鸟格复刻面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P20" s="5" t="str">
+        <v>BMW 宝马千鸟格复刻面料，德国复刻羊毛混纺千鸟格，适用于宝马 2002、E21、E28、E30 座椅与门板修复。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="21" spans="1:15" ht="137" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>189</v>
       </c>
@@ -3307,11 +3503,20 @@
         <v>194</v>
       </c>
       <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="1:15" ht="168" customHeight="1">
+      <c r="M21" s="5" t="str">
+        <v>Mercedes-Benz 奔驰千鸟格复刻面料</v>
+      </c>
+      <c r="N21" s="5" t="str">
+        <v>这款双色千鸟格面料参照 20 世纪 60 年代初奔驰中型车的原有规格织造，适用于 W110“尾鳍”轿车的内饰修复，包括 190c、190Dc 和早期 220 车型。</v>
+      </c>
+      <c r="O21" s="5" t="str">
+        <v>Mercedes-Benz 奔驰千鸟格复刻面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P21" s="5" t="str">
+        <v>Mercedes-Benz 奔驰千鸟格复刻面料，双色千鸟格复刻，适用于奔驰 W110 尾鳍车型 190c、190Dc 和早期 220。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="22" spans="1:15" ht="168" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>195</v>
       </c>
@@ -3338,11 +3543,20 @@
         <v>200</v>
       </c>
       <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="1:15" ht="75" customHeight="1">
+      <c r="M22" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料</v>
+      </c>
+      <c r="N22" s="5" t="str">
+        <v>参照 1968—1979 年 Volkswagen 大众 Type 2 Westfalia 露营车原有规格制作的内饰复刻面料，以厚实、密实的织法呈现经典方格图案。</v>
+      </c>
+      <c r="O22" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P22" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料，适用于大众 T2 Westfalia 露营车座椅与折叠床的经典格纹复刻布料。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="23" spans="1:15" ht="75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>201</v>
       </c>
@@ -3367,8 +3581,20 @@
       <c r="K23" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="24" spans="1:15" ht="30" customHeight="1">
+      <c r="M23" s="5" t="str">
+        <v>Ferrari 法拉利技术面料</v>
+      </c>
+      <c r="N23" s="5" t="str">
+        <v>用于 Ferrari 法拉利 488 Pista、812 Superfast 等车型的原版技术面料。这类合成纺织材料注重赛车运动性能，满足性能导向的汽车内饰需求。</v>
+      </c>
+      <c r="O23" s="5" t="str">
+        <v>Ferrari 法拉利技术面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P23" s="5" t="str">
+        <v>Ferrari 法拉利技术面料，面向赛车座椅拼片及汽车内饰的技术纺织材料，提供材质与规格信息。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="24" spans="1:15" ht="40" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>632</v>
       </c>
@@ -3401,6 +3627,18 @@
       </c>
       <c r="K24" t="s">
         <v>642</v>
+      </c>
+      <c r="M24" s="5" t="str">
+        <v>3D 立体间隔汽车面料</v>
+      </c>
+      <c r="N24" s="5" t="str">
+        <v>采用 3D 针织间隔结构的高性能技术面料，主要用于赛道取向车型及现代公路车型的座椅拼片、门板内衬和轻量化碳纤维赛车桶椅。</v>
+      </c>
+      <c r="O24" s="5" t="str">
+        <v>3D 立体间隔汽车面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P24" s="5" t="str">
+        <v>3D 立体间隔汽车面料，3D 针织间隔结构，兼顾透气、侧向抓附和缓冲，适用于座椅及门板内衬。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
       </c>
     </row>
     <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="25" spans="1:15" ht="90">
@@ -3436,6 +3674,18 @@
       </c>
       <c r="K25" t="s">
         <v>646</v>
+      </c>
+      <c r="M25" s="5" t="str">
+        <v>SuperFabric 高耐磨复合面料</v>
+      </c>
+      <c r="N25" s="5" t="str">
+        <v>SuperFabric® 是高性能复合材料，在保留常规织物柔韧性、透气性及重量特点的同时，提供较高的耐磨、耐切割、耐划割及耐穿刺性能。</v>
+      </c>
+      <c r="O25" s="5" t="str">
+        <v>SuperFabric 高耐磨复合面料｜规格与选材｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="P25" s="5" t="str">
+        <v>SuperFabric 高耐磨复合面料，陶瓷微型防护片结构，兼顾耐磨、耐穿刺与柔韧性，适用于汽车内饰。查看 CAMARI 卡玛瑞的配色、技术规格与选材资料。</v>
       </c>
     </row>
   </sheetData>
@@ -3446,9 +3696,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
+  <cols xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <col min="1" max="1" width="34.1640625" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
     <col min="3" max="3" width="19.33203125" customWidth="1"/>
@@ -3456,9 +3706,11 @@
     <col min="5" max="5" width="17.6640625" customWidth="1"/>
     <col min="7" max="7" width="19.83203125" customWidth="1"/>
     <col min="8" max="8" width="24.33203125" customWidth="1"/>
+    <col min="9" max="9" width="48" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="95" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3483,8 +3735,14 @@
       <c r="H1" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1">
+      <c r="I1" s="0" t="str">
+        <v>label_zh</v>
+      </c>
+      <c r="J1" s="0" t="str">
+        <v>default_value_zh</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="2" spans="1:8" ht="24" customHeight="1">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -3506,8 +3764,14 @@
       <c r="H2" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J2" s="5" t="str">
+        <v>0.6mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="3" spans="1:8" ht="24" customHeight="1">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -3529,8 +3793,14 @@
       <c r="H3" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="4" spans="1:8" ht="24" customHeight="1">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3552,8 +3822,14 @@
       <c r="H4" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J4" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="5" spans="1:8" ht="24" customHeight="1">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3575,8 +3851,14 @@
       <c r="H5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J5" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="6" spans="1:8" ht="24" customHeight="1">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3598,8 +3880,14 @@
       <c r="H6" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1">
+      <c r="I6" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J6" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="7" spans="1:8" ht="24" customHeight="1">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -3621,8 +3909,14 @@
       <c r="H7" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1">
+      <c r="I7" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J7" s="5" t="str">
+        <v>2.0mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="8" spans="1:8" ht="24" customHeight="1">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3644,8 +3938,14 @@
       <c r="H8" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1">
+      <c r="I8" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J8" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="9" spans="1:8" ht="24" customHeight="1">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -3667,8 +3967,14 @@
       <c r="H9" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1">
+      <c r="I9" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J9" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="10" spans="1:8" ht="24" customHeight="1">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -3690,8 +3996,14 @@
       <c r="H10" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1">
+      <c r="I10" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J10" s="5" t="str">
+        <v>聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="11" spans="1:8" ht="24" customHeight="1">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -3713,8 +4025,14 @@
       <c r="H11" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1">
+      <c r="I11" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J11" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="12" spans="1:8" ht="24" customHeight="1">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -3736,8 +4054,14 @@
       <c r="H12" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1">
+      <c r="I12" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J12" s="5" t="str">
+        <v>0.8mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="13" spans="1:8" ht="24" customHeight="1">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -3759,8 +4083,14 @@
       <c r="H13" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1">
+      <c r="I13" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J13" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="14" spans="1:8" ht="24" customHeight="1">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -3782,8 +4112,14 @@
       <c r="H14" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1">
+      <c r="I14" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J14" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="15" spans="1:8" ht="24" customHeight="1">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -3805,8 +4141,14 @@
       <c r="H15" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1">
+      <c r="I15" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J15" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="16" spans="1:8" ht="24" customHeight="1">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -3828,8 +4170,14 @@
       <c r="H16" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1">
+      <c r="I16" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J16" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="17" spans="1:8" ht="24" customHeight="1">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -3851,8 +4199,14 @@
       <c r="H17" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1">
+      <c r="I17" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J17" s="5" t="str">
+        <v>1.3mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="18" spans="1:8" ht="24" customHeight="1">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -3874,8 +4228,14 @@
       <c r="H18" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1">
+      <c r="I18" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J18" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="19" spans="1:8" ht="24" customHeight="1">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -3897,8 +4257,14 @@
       <c r="H19" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1">
+      <c r="I19" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J19" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="20" spans="1:8" ht="24" customHeight="1">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -3920,8 +4286,14 @@
       <c r="H20" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1">
+      <c r="I20" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J20" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="21" spans="1:8" ht="24" customHeight="1">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -3943,8 +4315,14 @@
       <c r="H21" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1">
+      <c r="I21" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J21" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -3966,8 +4344,14 @@
       <c r="H22" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J22" s="5" t="str">
+        <v>1.0mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="23" spans="1:8" ht="24" customHeight="1">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -3989,8 +4373,14 @@
       <c r="H23" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J23" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="24" spans="1:8" ht="24" customHeight="1">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -4012,8 +4402,14 @@
       <c r="H24" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J24" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="25" spans="1:8" ht="24" customHeight="1">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -4035,8 +4431,14 @@
       <c r="H25" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="I25" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J25" s="5" t="str">
+        <v>聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="26" spans="1:8" ht="24" customHeight="1">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -4058,8 +4460,14 @@
       <c r="H26" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="I26" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J26" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="27" spans="1:8" ht="24" customHeight="1">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -4081,8 +4489,14 @@
       <c r="H27" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="I27" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J27" s="5" t="str">
+        <v>0.8mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="28" spans="1:8" ht="24" customHeight="1">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -4104,8 +4518,14 @@
       <c r="H28" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="I28" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J28" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="29" spans="1:8" ht="24" customHeight="1">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -4127,8 +4547,14 @@
       <c r="H29" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="I29" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J29" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="30" spans="1:8" ht="24" customHeight="1">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -4150,8 +4576,14 @@
       <c r="H30" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="I30" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J30" s="5" t="str">
+        <v>羊毛</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="31" spans="1:8" ht="24" customHeight="1">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -4173,8 +4605,14 @@
       <c r="H31" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="I31" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J31" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="32" spans="1:8" ht="24" customHeight="1">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -4196,8 +4634,14 @@
       <c r="H32" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="I32" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J32" s="5" t="str">
+        <v>1.3mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="33" spans="1:8" ht="24" customHeight="1">
       <c r="A33" t="s">
         <v>73</v>
       </c>
@@ -4219,8 +4663,14 @@
       <c r="H33" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="I33" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J33" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="34" spans="1:8" ht="24" customHeight="1">
       <c r="A34" t="s">
         <v>73</v>
       </c>
@@ -4242,8 +4692,14 @@
       <c r="H34" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="I34" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J34" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="35" spans="1:8" ht="24" customHeight="1">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -4265,8 +4721,14 @@
       <c r="H35" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="I35" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J35" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="36" spans="1:8" ht="24" customHeight="1">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -4288,8 +4750,14 @@
       <c r="H36" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="I36" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J36" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="37" spans="1:8" ht="24" customHeight="1">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -4311,8 +4779,14 @@
       <c r="H37" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="I37" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J37" s="5" t="str">
+        <v>1.2mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="38" spans="1:8" ht="24" customHeight="1">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -4334,8 +4808,14 @@
       <c r="H38" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="I38" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J38" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="39" spans="1:8" ht="24" customHeight="1">
       <c r="A39" t="s">
         <v>82</v>
       </c>
@@ -4357,8 +4837,14 @@
       <c r="H39" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="40" spans="1:8">
+      <c r="I39" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J39" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="40" spans="1:8" ht="24" customHeight="1">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -4380,8 +4866,14 @@
       <c r="H40" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="41" spans="1:8">
+      <c r="I40" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J40" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="41" spans="1:8" ht="24" customHeight="1">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -4403,8 +4895,14 @@
       <c r="H41" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="42" spans="1:8">
+      <c r="I41" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J41" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="42" spans="1:8" ht="24" customHeight="1">
       <c r="A42" t="s">
         <v>92</v>
       </c>
@@ -4426,8 +4924,14 @@
       <c r="H42" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="43" spans="1:8">
+      <c r="I42" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J42" s="5" t="str">
+        <v>1.1mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="43" spans="1:8" ht="24" customHeight="1">
       <c r="A43" t="s">
         <v>92</v>
       </c>
@@ -4449,8 +4953,14 @@
       <c r="H43" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="I43" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J43" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="44" spans="1:8" ht="24" customHeight="1">
       <c r="A44" t="s">
         <v>92</v>
       </c>
@@ -4472,8 +4982,14 @@
       <c r="H44" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="45" spans="1:8">
+      <c r="I44" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J44" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="45" spans="1:8" ht="24" customHeight="1">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -4495,8 +5011,14 @@
       <c r="H45" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="46" spans="1:8">
+      <c r="I45" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J45" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="46" spans="1:8" ht="24" customHeight="1">
       <c r="A46" t="s">
         <v>92</v>
       </c>
@@ -4518,8 +5040,14 @@
       <c r="H46" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="47" spans="1:8">
+      <c r="I46" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J46" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="47" spans="1:8" ht="24" customHeight="1">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -4541,8 +5069,14 @@
       <c r="H47" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="I47" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J47" s="5" t="str">
+        <v>1.1mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="48" spans="1:8" ht="24" customHeight="1">
       <c r="A48" t="s">
         <v>102</v>
       </c>
@@ -4564,8 +5098,14 @@
       <c r="H48" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="I48" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J48" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="49" spans="1:8" ht="24" customHeight="1">
       <c r="A49" t="s">
         <v>102</v>
       </c>
@@ -4587,8 +5127,14 @@
       <c r="H49" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="I49" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J49" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="50" spans="1:8" ht="24" customHeight="1">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -4610,8 +5156,14 @@
       <c r="H50" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="I50" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J50" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="51" spans="1:8" ht="24" customHeight="1">
       <c r="A51" t="s">
         <v>102</v>
       </c>
@@ -4633,8 +5185,14 @@
       <c r="H51" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="52" spans="1:8">
+      <c r="I51" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J51" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="52" spans="1:8" ht="24" customHeight="1">
       <c r="A52" t="s">
         <v>112</v>
       </c>
@@ -4656,8 +5214,14 @@
       <c r="H52" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="53" spans="1:8">
+      <c r="I52" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J52" s="5" t="str">
+        <v>1.0mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="53" spans="1:8" ht="24" customHeight="1">
       <c r="A53" t="s">
         <v>112</v>
       </c>
@@ -4679,8 +5243,14 @@
       <c r="H53" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="54" spans="1:8">
+      <c r="I53" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J53" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="54" spans="1:8" ht="24" customHeight="1">
       <c r="A54" t="s">
         <v>112</v>
       </c>
@@ -4702,8 +5272,14 @@
       <c r="H54" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="55" spans="1:8">
+      <c r="I54" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J54" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="55" spans="1:8" ht="24" customHeight="1">
       <c r="A55" t="s">
         <v>112</v>
       </c>
@@ -4725,8 +5301,14 @@
       <c r="H55" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="I55" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J55" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="56" spans="1:8" ht="24" customHeight="1">
       <c r="A56" t="s">
         <v>112</v>
       </c>
@@ -4748,8 +5330,14 @@
       <c r="H56" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="I56" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J56" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="57" spans="1:8" ht="24" customHeight="1">
       <c r="A57" t="s">
         <v>122</v>
       </c>
@@ -4771,8 +5359,14 @@
       <c r="H57" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="58" spans="1:8">
+      <c r="I57" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J57" s="5" t="str">
+        <v>1.0mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="58" spans="1:8" ht="24" customHeight="1">
       <c r="A58" t="s">
         <v>122</v>
       </c>
@@ -4794,8 +5388,14 @@
       <c r="H58" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="59" spans="1:8">
+      <c r="I58" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J58" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="59" spans="1:8" ht="24" customHeight="1">
       <c r="A59" t="s">
         <v>122</v>
       </c>
@@ -4817,8 +5417,14 @@
       <c r="H59" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="60" spans="1:8">
+      <c r="I59" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J59" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="60" spans="1:8" ht="24" customHeight="1">
       <c r="A60" t="s">
         <v>122</v>
       </c>
@@ -4840,8 +5446,14 @@
       <c r="H60" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="61" spans="1:8">
+      <c r="I60" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J60" s="5" t="str">
+        <v>羊毛</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="61" spans="1:8" ht="24" customHeight="1">
       <c r="A61" t="s">
         <v>122</v>
       </c>
@@ -4863,8 +5475,14 @@
       <c r="H61" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="62" spans="1:8">
+      <c r="I61" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J61" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="62" spans="1:8" ht="24" customHeight="1">
       <c r="A62" t="s">
         <v>127</v>
       </c>
@@ -4886,8 +5504,14 @@
       <c r="H62" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="63" spans="1:8">
+      <c r="I62" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J62" s="5" t="str">
+        <v>1.6mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="63" spans="1:8" ht="24" customHeight="1">
       <c r="A63" t="s">
         <v>127</v>
       </c>
@@ -4909,8 +5533,14 @@
       <c r="H63" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="64" spans="1:8">
+      <c r="I63" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J63" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="64" spans="1:8" ht="24" customHeight="1">
       <c r="A64" t="s">
         <v>127</v>
       </c>
@@ -4932,8 +5562,14 @@
       <c r="H64" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="65" spans="1:8">
+      <c r="I64" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J64" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="65" spans="1:8" ht="24" customHeight="1">
       <c r="A65" t="s">
         <v>127</v>
       </c>
@@ -4955,8 +5591,14 @@
       <c r="H65" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="66" spans="1:8">
+      <c r="I65" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J65" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="66" spans="1:8" ht="24" customHeight="1">
       <c r="A66" t="s">
         <v>127</v>
       </c>
@@ -4978,8 +5620,14 @@
       <c r="H66" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="67" spans="1:8">
+      <c r="I66" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J66" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="67" spans="1:8" ht="24" customHeight="1">
       <c r="A67" t="s">
         <v>137</v>
       </c>
@@ -5001,8 +5649,14 @@
       <c r="H67" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="68" spans="1:8">
+      <c r="I67" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J67" s="5" t="str">
+        <v>1.3mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="68" spans="1:8" ht="24" customHeight="1">
       <c r="A68" t="s">
         <v>137</v>
       </c>
@@ -5024,8 +5678,14 @@
       <c r="H68" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="69" spans="1:8">
+      <c r="I68" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J68" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="69" spans="1:8" ht="24" customHeight="1">
       <c r="A69" t="s">
         <v>137</v>
       </c>
@@ -5047,8 +5707,14 @@
       <c r="H69" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="70" spans="1:8">
+      <c r="I69" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J69" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="70" spans="1:8" ht="24" customHeight="1">
       <c r="A70" t="s">
         <v>137</v>
       </c>
@@ -5070,8 +5736,14 @@
       <c r="H70" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="71" spans="1:8">
+      <c r="I70" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J70" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="71" spans="1:8" ht="24" customHeight="1">
       <c r="A71" t="s">
         <v>137</v>
       </c>
@@ -5093,8 +5765,14 @@
       <c r="H71" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="72" spans="1:8">
+      <c r="I71" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J71" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="72" spans="1:8" ht="24" customHeight="1">
       <c r="A72" t="s">
         <v>147</v>
       </c>
@@ -5116,8 +5794,14 @@
       <c r="H72" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="73" spans="1:8">
+      <c r="I72" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J72" s="5" t="str">
+        <v>1.3mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="73" spans="1:8" ht="24" customHeight="1">
       <c r="A73" t="s">
         <v>147</v>
       </c>
@@ -5139,8 +5823,14 @@
       <c r="H73" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="74" spans="1:8">
+      <c r="I73" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J73" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="74" spans="1:8" ht="24" customHeight="1">
       <c r="A74" t="s">
         <v>147</v>
       </c>
@@ -5162,8 +5852,14 @@
       <c r="H74" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="75" spans="1:8">
+      <c r="I74" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J74" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="75" spans="1:8" ht="24" customHeight="1">
       <c r="A75" t="s">
         <v>147</v>
       </c>
@@ -5185,8 +5881,14 @@
       <c r="H75" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="76" spans="1:8">
+      <c r="I75" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J75" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="76" spans="1:8" ht="24" customHeight="1">
       <c r="A76" t="s">
         <v>147</v>
       </c>
@@ -5208,8 +5910,14 @@
       <c r="H76" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="77" spans="1:8">
+      <c r="I76" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J76" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="77" spans="1:8" ht="24" customHeight="1">
       <c r="A77" t="s">
         <v>157</v>
       </c>
@@ -5231,8 +5939,14 @@
       <c r="H77" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="78" spans="1:8">
+      <c r="I77" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J77" s="5" t="str">
+        <v>1.0mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="78" spans="1:8" ht="24" customHeight="1">
       <c r="A78" t="s">
         <v>157</v>
       </c>
@@ -5254,8 +5968,14 @@
       <c r="H78" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="79" spans="1:8">
+      <c r="I78" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J78" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="79" spans="1:8" ht="24" customHeight="1">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -5277,8 +5997,14 @@
       <c r="H79" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="80" spans="1:8">
+      <c r="I79" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J79" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="80" spans="1:8" ht="24" customHeight="1">
       <c r="A80" t="s">
         <v>157</v>
       </c>
@@ -5300,8 +6026,14 @@
       <c r="H80" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="81" spans="1:8">
+      <c r="I80" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J80" s="5" t="str">
+        <v>聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="81" spans="1:8" ht="24" customHeight="1">
       <c r="A81" t="s">
         <v>157</v>
       </c>
@@ -5323,8 +6055,14 @@
       <c r="H81" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="82" spans="1:8">
+      <c r="I81" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J81" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="82" spans="1:8" ht="24" customHeight="1">
       <c r="A82" t="s">
         <v>167</v>
       </c>
@@ -5346,8 +6084,14 @@
       <c r="H82" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="83" spans="1:8">
+      <c r="I82" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J82" s="5" t="str">
+        <v>0.6mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="83" spans="1:8" ht="24" customHeight="1">
       <c r="A83" t="s">
         <v>167</v>
       </c>
@@ -5369,8 +6113,14 @@
       <c r="H83" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="84" spans="1:8">
+      <c r="I83" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J83" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="84" spans="1:8" ht="24" customHeight="1">
       <c r="A84" t="s">
         <v>167</v>
       </c>
@@ -5392,8 +6142,14 @@
       <c r="H84" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="85" spans="1:8">
+      <c r="I84" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J84" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="85" spans="1:8" ht="24" customHeight="1">
       <c r="A85" t="s">
         <v>167</v>
       </c>
@@ -5415,8 +6171,14 @@
       <c r="H85" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="86" spans="1:8">
+      <c r="I85" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J85" s="5" t="str">
+        <v>羊毛</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="86" spans="1:8" ht="24" customHeight="1">
       <c r="A86" t="s">
         <v>167</v>
       </c>
@@ -5438,8 +6200,14 @@
       <c r="H86" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="87" spans="1:8">
+      <c r="I86" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J86" s="5" t="str">
+        <v>英国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="87" spans="1:8" ht="24" customHeight="1">
       <c r="A87" t="s">
         <v>177</v>
       </c>
@@ -5461,8 +6229,14 @@
       <c r="H87" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="88" spans="1:8">
+      <c r="I87" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J87" s="5" t="str">
+        <v>1.0mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="88" spans="1:8" ht="24" customHeight="1">
       <c r="A88" t="s">
         <v>177</v>
       </c>
@@ -5484,8 +6258,14 @@
       <c r="H88" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="89" spans="1:8">
+      <c r="I88" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J88" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="89" spans="1:8" ht="24" customHeight="1">
       <c r="A89" t="s">
         <v>177</v>
       </c>
@@ -5507,8 +6287,14 @@
       <c r="H89" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="90" spans="1:8">
+      <c r="I89" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J89" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="90" spans="1:8" ht="24" customHeight="1">
       <c r="A90" t="s">
         <v>177</v>
       </c>
@@ -5530,8 +6316,14 @@
       <c r="H90" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="91" spans="1:8">
+      <c r="I90" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J90" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="91" spans="1:8" ht="24" customHeight="1">
       <c r="A91" t="s">
         <v>177</v>
       </c>
@@ -5553,8 +6345,14 @@
       <c r="H91" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1">
+      <c r="I91" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J91" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="92" spans="1:8" ht="24" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>183</v>
       </c>
@@ -5576,8 +6374,14 @@
       <c r="H92" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1">
+      <c r="I92" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J92" s="5" t="str">
+        <v>1.1mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="93" spans="1:8" ht="24" customHeight="1">
       <c r="A93" s="1" t="s">
         <v>183</v>
       </c>
@@ -5599,8 +6403,14 @@
       <c r="H93" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1">
+      <c r="I93" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J93" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="94" spans="1:8" ht="24" customHeight="1">
       <c r="A94" s="1" t="s">
         <v>183</v>
       </c>
@@ -5622,8 +6432,14 @@
       <c r="H94" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1">
+      <c r="I94" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J94" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="95" spans="1:8" ht="24" customHeight="1">
       <c r="A95" s="1" t="s">
         <v>183</v>
       </c>
@@ -5645,8 +6461,14 @@
       <c r="H95" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1">
+      <c r="I95" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J95" s="5" t="str">
+        <v>羊毛／聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="96" spans="1:8" ht="24" customHeight="1">
       <c r="A96" s="1" t="s">
         <v>183</v>
       </c>
@@ -5668,8 +6490,14 @@
       <c r="H96" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1">
+      <c r="I96" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J96" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="97" spans="1:8" ht="24" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>189</v>
       </c>
@@ -5691,8 +6519,14 @@
       <c r="H97" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1">
+      <c r="I97" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J97" s="5" t="str">
+        <v>1.0mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="98" spans="1:8" ht="24" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>189</v>
       </c>
@@ -5714,8 +6548,14 @@
       <c r="H98" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" ht="15" customHeight="1">
+      <c r="I98" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J98" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="99" spans="1:8" ht="24" customHeight="1">
       <c r="A99" s="1" t="s">
         <v>189</v>
       </c>
@@ -5737,8 +6577,14 @@
       <c r="H99" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" ht="15" customHeight="1">
+      <c r="I99" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J99" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="100" spans="1:8" ht="24" customHeight="1">
       <c r="A100" s="1" t="s">
         <v>189</v>
       </c>
@@ -5760,8 +6606,14 @@
       <c r="H100" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1">
+      <c r="I100" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J100" s="5" t="str">
+        <v>羊毛</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="101" spans="1:8" ht="24" customHeight="1">
       <c r="A101" s="1" t="s">
         <v>189</v>
       </c>
@@ -5783,8 +6635,14 @@
       <c r="H101" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1">
+      <c r="I101" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J101" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="102" spans="1:8" ht="24" customHeight="1">
       <c r="A102" s="1" t="s">
         <v>195</v>
       </c>
@@ -5806,8 +6664,14 @@
       <c r="H102" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1">
+      <c r="I102" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J102" s="5" t="str">
+        <v>0.9mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="103" spans="1:8" ht="24" customHeight="1">
       <c r="A103" s="1" t="s">
         <v>195</v>
       </c>
@@ -5829,8 +6693,14 @@
       <c r="H103" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1">
+      <c r="I103" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J103" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="104" spans="1:8" ht="24" customHeight="1">
       <c r="A104" s="1" t="s">
         <v>195</v>
       </c>
@@ -5852,8 +6722,14 @@
       <c r="H104" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1">
+      <c r="I104" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J104" s="5" t="str">
+        <v>140CM</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="105" spans="1:8" ht="24" customHeight="1">
       <c r="A105" s="1" t="s">
         <v>195</v>
       </c>
@@ -5875,8 +6751,14 @@
       <c r="H105" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" ht="15" customHeight="1">
+      <c r="I105" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J105" s="5" t="str">
+        <v>聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="106" spans="1:8" ht="24" customHeight="1">
       <c r="A106" s="1" t="s">
         <v>195</v>
       </c>
@@ -5898,8 +6780,14 @@
       <c r="H106" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" ht="15" customHeight="1">
+      <c r="I106" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J106" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="107" spans="1:8" ht="24" customHeight="1">
       <c r="A107" s="1" t="s">
         <v>201</v>
       </c>
@@ -5921,8 +6809,14 @@
       <c r="H107" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" ht="15" customHeight="1">
+      <c r="I107" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J107" s="5" t="str">
+        <v>0.85mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="108" spans="1:8" ht="24" customHeight="1">
       <c r="A108" s="1" t="s">
         <v>201</v>
       </c>
@@ -5944,8 +6838,14 @@
       <c r="H108" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" ht="15" customHeight="1">
+      <c r="I108" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J108" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="109" spans="1:8" ht="24" customHeight="1">
       <c r="A109" s="1" t="s">
         <v>201</v>
       </c>
@@ -5967,8 +6867,14 @@
       <c r="H109" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" ht="15" customHeight="1">
+      <c r="I109" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J109" s="5" t="str">
+        <v>140cm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="110" spans="1:8" ht="24" customHeight="1">
       <c r="A110" s="1" t="s">
         <v>201</v>
       </c>
@@ -5990,8 +6896,14 @@
       <c r="H110" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" ht="15" customHeight="1">
+      <c r="I110" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J110" s="5" t="str">
+        <v>聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="111" spans="1:8" ht="24" customHeight="1">
       <c r="A111" s="1" t="s">
         <v>201</v>
       </c>
@@ -6013,8 +6925,14 @@
       <c r="H111" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="112" spans="1:8" ht="15">
+      <c r="I111" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J111" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="112" spans="1:8" ht="24" customHeight="1">
       <c r="A112" s="1" t="s">
         <v>632</v>
       </c>
@@ -6036,8 +6954,14 @@
       <c r="H112" t="str">
         <v>1.7mm</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="113" spans="1:7" ht="15">
+      <c r="I112" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J112" s="5" t="str">
+        <v>1.7mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="113" spans="1:7" ht="24" customHeight="1">
       <c r="A113" s="1" t="s">
         <v>632</v>
       </c>
@@ -6059,8 +6983,14 @@
       <c r="H113" t="str">
         <v>自動車用</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="114" spans="1:7" ht="15">
+      <c r="I113" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J113" s="5" t="str">
+        <v>汽车内饰</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="114" spans="1:7" ht="24" customHeight="1">
       <c r="A114" s="1" t="s">
         <v>631</v>
       </c>
@@ -6082,8 +7012,14 @@
       <c r="H114" t="str">
         <v>140cm</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="115" spans="1:7" ht="15">
+      <c r="I114" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J114" s="5" t="str">
+        <v>140cm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="115" spans="1:7" ht="24" customHeight="1">
       <c r="A115" s="1" t="s">
         <v>631</v>
       </c>
@@ -6105,8 +7041,14 @@
       <c r="H115" t="str">
         <v>ポリエステル</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="116" spans="1:7" ht="15">
+      <c r="I115" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="J115" s="5" t="str">
+        <v>聚酯纤维</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="116" spans="1:7" ht="24" customHeight="1">
       <c r="A116" s="1" t="s">
         <v>631</v>
       </c>
@@ -6128,8 +7070,14 @@
       <c r="H116" t="str">
         <v>ドイツ</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="117" spans="1:7" ht="15">
+      <c r="I116" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J116" s="5" t="str">
+        <v>德国</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="117" spans="1:7" ht="24" customHeight="1">
       <c r="A117" s="1" t="s">
         <v>633</v>
       </c>
@@ -6151,8 +7099,14 @@
       <c r="H117" t="str">
         <v>1.1mm</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="118" spans="1:7" ht="15">
+      <c r="I117" s="5" t="str">
+        <v>厚度</v>
+      </c>
+      <c r="J117" s="5" t="str">
+        <v>1.1mm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="118" spans="1:7" ht="24" customHeight="1">
       <c r="A118" s="1" t="s">
         <v>633</v>
       </c>
@@ -6174,8 +7128,14 @@
       <c r="H118" t="str">
         <v>自動車・アクセサリー用</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="119" spans="1:7" ht="15">
+      <c r="I118" s="5" t="str">
+        <v>用途</v>
+      </c>
+      <c r="J118" s="5" t="str">
+        <v>汽车内饰／配件</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="119" spans="1:7" ht="24" customHeight="1">
       <c r="A119" s="1" t="s">
         <v>633</v>
       </c>
@@ -6197,8 +7157,14 @@
       <c r="H119" t="str">
         <v>132cm</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="120" spans="1:7" ht="15">
+      <c r="I119" s="5" t="str">
+        <v>幅宽</v>
+      </c>
+      <c r="J119" s="5" t="str">
+        <v>132cm</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="120" spans="1:7" ht="24" customHeight="1">
       <c r="A120" s="1" t="s">
         <v>633</v>
       </c>
@@ -6220,8 +7186,14 @@
       <c r="H120" t="str">
         <v>450g/m²</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="121" spans="1:7" ht="15">
+      <c r="I120" s="5" t="str">
+        <v>单位面积质量</v>
+      </c>
+      <c r="J120" s="5" t="str">
+        <v>450 g/m²</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="121" spans="1:7" ht="24" customHeight="1">
       <c r="A121" s="1" t="s">
         <v>633</v>
       </c>
@@ -6243,8 +7215,14 @@
       <c r="H121" t="str">
         <v>1814g</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="122" spans="1:7" ht="15">
+      <c r="I121" s="5" t="str">
+        <v>耐切割性</v>
+      </c>
+      <c r="J121" s="5" t="str">
+        <v>1814g</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="122" spans="1:7" ht="24" customHeight="1">
       <c r="A122" s="1" t="s">
         <v>633</v>
       </c>
@@ -6266,8 +7244,14 @@
       <c r="H122" t="str">
         <v>3000回</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="123" spans="1:7" ht="15">
+      <c r="I122" s="5" t="str">
+        <v>耐磨性</v>
+      </c>
+      <c r="J122" s="5" t="str">
+        <v>3000次</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="123" spans="1:7" ht="24" customHeight="1">
       <c r="A123" s="1" t="s">
         <v>633</v>
       </c>
@@ -6288,6 +7272,12 @@
       </c>
       <c r="H123" t="str">
         <v>米国</v>
+      </c>
+      <c r="I123" s="5" t="str">
+        <v>原产国</v>
+      </c>
+      <c r="J123" s="5" t="str">
+        <v>美国</v>
       </c>
     </row>
   </sheetData>
@@ -6298,10 +7288,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <col min="5" max="5" width="70" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6313,6 +7306,9 @@
       </c>
       <c r="D1" t="s">
         <v>255</v>
+      </c>
+      <c r="E1" s="0" t="str">
+        <v>text_zh</v>
       </c>
     </row>
   </sheetData>
@@ -6323,10 +7319,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <col min="7" max="7" width="70" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="95" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6344,6 +7344,12 @@
       </c>
       <c r="F1" t="s">
         <v>259</v>
+      </c>
+      <c r="G1" s="0" t="str">
+        <v>title_zh</v>
+      </c>
+      <c r="H1" s="0" t="str">
+        <v>description_zh</v>
       </c>
     </row>
   </sheetData>
@@ -6354,9 +7360,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:U58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
+  <cols xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="3" max="3" width="20.1640625" customWidth="1"/>
     <col min="5" max="5" width="36.83203125" customWidth="1"/>
@@ -6369,9 +7375,13 @@
     <col min="14" max="14" width="21.83203125" customWidth="1"/>
     <col min="15" max="15" width="22.33203125" customWidth="1"/>
     <col min="16" max="16" width="36.6640625" customWidth="1"/>
+    <col min="18" max="18" width="34" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="95" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="78" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="95" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1" spans="1:17">
       <c r="A1" t="s">
         <v>260</v>
       </c>
@@ -6423,8 +7433,20 @@
       <c r="Q1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="0" t="str">
+        <v>color_name_zh</v>
+      </c>
+      <c r="S1" s="0" t="str">
+        <v>summary_zh</v>
+      </c>
+      <c r="T1" s="0" t="str">
+        <v>seo_title_zh</v>
+      </c>
+      <c r="U1" s="0" t="str">
+        <v>seo_description_zh</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="2" spans="1:17" ht="40" customHeight="1">
       <c r="A2" t="s">
         <v>268</v>
       </c>
@@ -6452,8 +7474,20 @@
       <c r="Q2" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" s="5" t="str">
+        <v>BLACK/GRAY/BROWN</v>
+      </c>
+      <c r="S2" s="5" t="str">
+        <v>BMW 宝马方格复刻面料，BLACK/GRAY/BROWN，编号 FA1836。适用于 BMW 宝马 Isetta 内饰的经典苏格兰方格面料。</v>
+      </c>
+      <c r="T2" s="5" t="str">
+        <v>BMW 宝马方格复刻面料 FA1836 BLACK/GRAY/BROWN｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U2" s="5" t="str">
+        <v>BMW 宝马方格复刻面料，编号 FA1836，配色BLACK/GRAY/BROWN。适用于 BMW 宝马 Isetta 内饰的经典苏格兰方格面料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="3" spans="1:17" ht="40" customHeight="1">
       <c r="A3" t="s">
         <v>273</v>
       </c>
@@ -6481,8 +7515,20 @@
       <c r="Q3" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="5" t="str">
+        <v>M PATTERN</v>
+      </c>
+      <c r="S3" s="5" t="str">
+        <v>BMW 宝马 M 条纹复刻面料，M PATTERN，编号 FA5990。M-Stripe 座椅面料复刻了 BMW 宝马 M8 原型车所使用的经典 M 条纹材料。</v>
+      </c>
+      <c r="T3" s="5" t="str">
+        <v>BMW 宝马 M 条纹复刻面料 FA5990 M PATTERN｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U3" s="5" t="str">
+        <v>BMW 宝马 M 条纹复刻面料，编号 FA5990，配色M PATTERN。M-Stripe 座椅面料复刻了 BMW 宝马 M8 原型车所使用的经典 M 条纹材料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="4" spans="1:17" ht="40" customHeight="1">
       <c r="A4" t="s">
         <v>278</v>
       </c>
@@ -6510,8 +7556,20 @@
       <c r="Q4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" s="5" t="str">
+        <v>GRAY/WHITE/BROWN</v>
+      </c>
+      <c r="S4" s="5" t="str">
+        <v>千鸟格复合格纹汽车面料，GRAY/WHITE/BROWN，编号 FA8765。以千鸟格为基础的格伦格纹融合苏格兰方格，形成细致的复合图案，适用于座椅软包。</v>
+      </c>
+      <c r="T4" s="5" t="str">
+        <v>千鸟格复合格纹汽车面料 FA8765 GRAY/WHITE/BROWN｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U4" s="5" t="str">
+        <v>千鸟格复合格纹汽车面料，编号 FA8765，配色GRAY/WHITE/BROWN。以千鸟格为基础的格伦格纹融合苏格兰方格，形成细致的复合图案，适用于座椅软包。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="5" spans="1:17" ht="40" customHeight="1">
       <c r="A5" t="s">
         <v>283</v>
       </c>
@@ -6539,8 +7597,20 @@
       <c r="Q5" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" s="5" t="str">
+        <v>BLACK/BROWN/RED</v>
+      </c>
+      <c r="S5" s="5" t="str">
+        <v>Mercedes-Benz 奔驰方格复刻面料，BLACK/BROWN/RED，编号 FA8475。参照第一代 Mercedes-Benz 奔驰 W460 G 级经典内饰规格与纹理制作的复刻面料。</v>
+      </c>
+      <c r="T5" s="5" t="str">
+        <v>Mercedes-Benz 奔驰方格复刻面料 FA8475 BLACK/BROWN/RED｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U5" s="5" t="str">
+        <v>Mercedes-Benz 奔驰方格复刻面料，编号 FA8475，配色BLACK/BROWN/RED。参照第一代 Mercedes-Benz 奔驰 W460 G 级经典内饰规格与纹理制作的复刻面料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="6" spans="1:17" ht="56" customHeight="1">
       <c r="A6" t="s">
         <v>288</v>
       </c>
@@ -6568,8 +7638,20 @@
       <c r="Q6" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" s="5" t="str">
+        <v>GRAY/BLACK</v>
+      </c>
+      <c r="S6" s="5" t="str">
+        <v>Mercedes-Benz 奔驰 Rodeo 复刻面料，GRAY/BLACK，编号 FA8598。参照 20 世纪 80 年代末 Mercedes-Benz 奔驰 G 级原车内饰纹理制作的 Rodeo 复刻面料。相同图案也用于 2025 年 G550“Stronger Than the 1980s”特别版。</v>
+      </c>
+      <c r="T6" s="5" t="str">
+        <v>Mercedes-Benz 奔驰 Rodeo 复刻面料 FA8598 GRAY/BLACK｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U6" s="5" t="str">
+        <v>Mercedes-Benz 奔驰 Rodeo 复刻面料，编号 FA8598，配色GRAY/BLACK。参照 20 世纪 80 年代末 Mercedes-Benz 奔驰 G 级原车内饰纹理制作的 Rodeo 复刻面料。相同图案也用于 2025 年 G550“Stronger Than the 1980s”特别版。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="7" spans="1:17" ht="56" customHeight="1">
       <c r="A7" t="s">
         <v>293</v>
       </c>
@@ -6597,8 +7679,20 @@
       <c r="Q7" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" s="5" t="str">
+        <v>BLUE/GRAY</v>
+      </c>
+      <c r="S7" s="5" t="str">
+        <v>Mercedes-Benz 奔驰纯羊毛格纹面料，BLUE/GRAY，编号 FA8626。采用 100% 纯羊毛织造，专为 Mercedes-Benz 奔驰 W198 300SL Gullwing 鸥翼车型的内饰修复选材设计。</v>
+      </c>
+      <c r="T7" s="5" t="str">
+        <v>Mercedes-Benz 奔驰纯羊毛格纹面料 FA8626 BLUE/GRAY｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U7" s="5" t="str">
+        <v>Mercedes-Benz 奔驰纯羊毛格纹面料，编号 FA8626，配色BLUE/GRAY。采用 100% 纯羊毛织造，专为 Mercedes-Benz 奔驰 W198 300SL Gullwing 鸥翼车型的内饰修复选材设计。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="8" spans="1:17" ht="56" customHeight="1">
       <c r="A8" t="s">
         <v>298</v>
       </c>
@@ -6626,8 +7720,20 @@
       <c r="Q8" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" s="5" t="str">
+        <v>GREEN/GRAY/WHITE</v>
+      </c>
+      <c r="S8" s="5" t="str">
+        <v>Mercedes-Benz 奔驰纯羊毛格纹面料，GREEN/GRAY/WHITE，编号 FA8637。采用 100% 纯羊毛织造，专为 Mercedes-Benz 奔驰 W198 300SL Gullwing 鸥翼车型的内饰修复选材设计。</v>
+      </c>
+      <c r="T8" s="5" t="str">
+        <v>Mercedes-Benz 奔驰纯羊毛格纹面料 FA8637 GREEN/GRAY/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U8" s="5" t="str">
+        <v>Mercedes-Benz 奔驰纯羊毛格纹面料，编号 FA8637，配色GREEN/GRAY/WHITE。采用 100% 纯羊毛织造，专为 Mercedes-Benz 奔驰 W198 300SL Gullwing 鸥翼车型的内饰修复选材设计。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="9" spans="1:17" ht="40" customHeight="1">
       <c r="A9" t="s">
         <v>303</v>
       </c>
@@ -6655,8 +7761,20 @@
       <c r="Q9" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" s="5" t="str">
+        <v>BLACK/BROWN/YELLOW</v>
+      </c>
+      <c r="S9" s="5" t="str">
+        <v>Porsche 保时捷方格复刻面料，BLACK/BROWN/YELLOW，编号 FA8045。适用于 Porsche 保时捷内饰软包的经典方格图案面料。</v>
+      </c>
+      <c r="T9" s="5" t="str">
+        <v>Porsche 保时捷方格复刻面料 FA8045 BLACK/BROWN/YELLOW｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U9" s="5" t="str">
+        <v>Porsche 保时捷方格复刻面料，编号 FA8045，配色BLACK/BROWN/YELLOW。适用于 Porsche 保时捷内饰软包的经典方格图案面料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="10" spans="1:17" ht="40" customHeight="1">
       <c r="A10" t="s">
         <v>308</v>
       </c>
@@ -6684,8 +7802,20 @@
       <c r="Q10" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" s="5" t="str">
+        <v>BROWN/TAN/GREEN</v>
+      </c>
+      <c r="S10" s="5" t="str">
+        <v>Porsche 保时捷方格复刻面料，BROWN/TAN/GREEN，编号 FA8057。适用于 Porsche 保时捷内饰软包的经典方格图案面料。</v>
+      </c>
+      <c r="T10" s="5" t="str">
+        <v>Porsche 保时捷方格复刻面料 FA8057 BROWN/TAN/GREEN｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U10" s="5" t="str">
+        <v>Porsche 保时捷方格复刻面料，编号 FA8057，配色BROWN/TAN/GREEN。适用于 Porsche 保时捷内饰软包的经典方格图案面料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="11" spans="1:17" ht="40" customHeight="1">
       <c r="A11" t="s">
         <v>313</v>
       </c>
@@ -6713,8 +7843,20 @@
       <c r="Q11" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" s="5" t="str">
+        <v>BLACK/WHITE/RED</v>
+      </c>
+      <c r="S11" s="5" t="str">
+        <v>Porsche 保时捷方格复刻面料，BLACK/WHITE/RED，编号 FA8063。适用于 Porsche 保时捷内饰软包的经典方格图案面料。</v>
+      </c>
+      <c r="T11" s="5" t="str">
+        <v>Porsche 保时捷方格复刻面料 FA8063 BLACK/WHITE/RED｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U11" s="5" t="str">
+        <v>Porsche 保时捷方格复刻面料，编号 FA8063，配色BLACK/WHITE/RED。适用于 Porsche 保时捷内饰软包的经典方格图案面料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="12" spans="1:17" ht="40" customHeight="1">
       <c r="A12" t="s">
         <v>318</v>
       </c>
@@ -6742,8 +7884,20 @@
       <c r="Q12" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" s="5" t="str">
+        <v>BLACK/WHITE</v>
+      </c>
+      <c r="S12" s="5" t="str">
+        <v>Porsche 保时捷人字纹复刻面料，BLACK/WHITE，编号 FA3570。参照 Porsche 保时捷 924 原车座椅规格与纹理制作的人字纹汽车内饰复刻面料。</v>
+      </c>
+      <c r="T12" s="5" t="str">
+        <v>Porsche 保时捷人字纹复刻面料 FA3570 BLACK/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U12" s="5" t="str">
+        <v>Porsche 保时捷人字纹复刻面料，编号 FA3570，配色BLACK/WHITE。参照 Porsche 保时捷 924 原车座椅规格与纹理制作的人字纹汽车内饰复刻面料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="13" spans="1:17" ht="56" customHeight="1">
       <c r="A13" t="s">
         <v>323</v>
       </c>
@@ -6771,8 +7925,20 @@
       <c r="Q13" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13" s="5" t="str">
+        <v>BLUE/WHITE</v>
+      </c>
+      <c r="S13" s="5" t="str">
+        <v>Porsche 保时捷 Madras 格纹面料，BLUE/WHITE，编号 FA8326。Madras 是 1972 至 1975 年间保时捷提供的经典内饰选装面料，曾用于早期 G-Model 911，包括 911T、911E、911S 及早期 Carrera 车型。</v>
+      </c>
+      <c r="T13" s="5" t="str">
+        <v>Porsche 保时捷 Madras 格纹面料 FA8326 BLUE/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U13" s="5" t="str">
+        <v>Porsche 保时捷 Madras 格纹面料，编号 FA8326，配色BLUE/WHITE。Madras 是 1972 至 1975 年间保时捷提供的经典内饰选装面料，曾用于早期 G-Model 911，包括 911T、911E、911S 及早期 Carrera 车型。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="14" spans="1:17" ht="56" customHeight="1">
       <c r="A14" t="s">
         <v>328</v>
       </c>
@@ -6800,8 +7966,20 @@
       <c r="Q14" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14" s="5" t="str">
+        <v>ORANGE/BROWN</v>
+      </c>
+      <c r="S14" s="5" t="str">
+        <v>Porsche 保时捷 Madras 格纹面料，ORANGE/BROWN，编号 FA8354。Madras 是 1972 至 1975 年间保时捷提供的经典内饰选装面料，曾用于早期 G-Model 911，包括 911T、911E、911S 及早期 Carrera 车型。</v>
+      </c>
+      <c r="T14" s="5" t="str">
+        <v>Porsche 保时捷 Madras 格纹面料 FA8354 ORANGE/BROWN｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U14" s="5" t="str">
+        <v>Porsche 保时捷 Madras 格纹面料，编号 FA8354，配色ORANGE/BROWN。Madras 是 1972 至 1975 年间保时捷提供的经典内饰选装面料，曾用于早期 G-Model 911，包括 911T、911E、911S 及早期 Carrera 车型。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="15" spans="1:17" ht="56" customHeight="1">
       <c r="A15" t="s">
         <v>333</v>
       </c>
@@ -6829,8 +8007,20 @@
       <c r="Q15" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15" s="5" t="str">
+        <v>BLACK/WHITE/ORANGE</v>
+      </c>
+      <c r="S15" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，BLACK/WHITE/ORANGE，编号 FA8013。Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。</v>
+      </c>
+      <c r="T15" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料 FA8013 BLACK/WHITE/ORANGE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U15" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，编号 FA8013，配色BLACK/WHITE/ORANGE。Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="16" spans="1:17" ht="56" customHeight="1">
       <c r="A16" t="s">
         <v>338</v>
       </c>
@@ -6858,8 +8048,20 @@
       <c r="Q16" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" s="5" t="str">
+        <v>BLACK/WHITE/BLUE</v>
+      </c>
+      <c r="S16" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，BLACK/WHITE/BLUE，编号 FA8026。Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。</v>
+      </c>
+      <c r="T16" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料 FA8026 BLACK/WHITE/BLUE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U16" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，编号 FA8026，配色BLACK/WHITE/BLUE。Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="17" spans="1:17" ht="56" customHeight="1">
       <c r="A17" t="s">
         <v>343</v>
       </c>
@@ -6887,8 +8089,20 @@
       <c r="Q17" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" s="5" t="str">
+        <v>BLACK/WHITE</v>
+      </c>
+      <c r="S17" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，BLACK/WHITE，编号 FA8065。Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。</v>
+      </c>
+      <c r="T17" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料 FA8065 BLACK/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U17" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，编号 FA8065，配色BLACK/WHITE。Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="18" spans="1:17" ht="56" customHeight="1">
       <c r="A18" t="s">
         <v>347</v>
       </c>
@@ -6916,8 +8130,20 @@
       <c r="Q18" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" s="5" t="str">
+        <v>BLACK/WHITE/BEIGE</v>
+      </c>
+      <c r="S18" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，BLACK/WHITE/BEIGE，编号 FA8074。Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。</v>
+      </c>
+      <c r="T18" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料 FA8074 BLACK/WHITE/BEIGE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U18" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，编号 FA8074，配色BLACK/WHITE/BEIGE。Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="19" spans="1:17" ht="56" customHeight="1">
       <c r="A19" t="s">
         <v>352</v>
       </c>
@@ -6945,8 +8171,20 @@
       <c r="Q19" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" s="5" t="str">
+        <v>BLACK/WHITE/GREEN</v>
+      </c>
+      <c r="S19" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，BLACK/WHITE/GREEN，编号 FA8093。Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。</v>
+      </c>
+      <c r="T19" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料 FA8093 BLACK/WHITE/GREEN｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U19" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，编号 FA8093，配色BLACK/WHITE/GREEN。Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="20" spans="1:17" ht="56" customHeight="1">
       <c r="A20" t="s">
         <v>357</v>
       </c>
@@ -6974,8 +8212,20 @@
       <c r="Q20" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" s="5" t="str">
+        <v>BLACK/WHITE/RED</v>
+      </c>
+      <c r="S20" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，BLACK/WHITE/RED，编号 FA8094。Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。</v>
+      </c>
+      <c r="T20" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料 FA8094 BLACK/WHITE/RED｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U20" s="5" t="str">
+        <v>Porsche 保时捷 Pepita 千鸟格面料，编号 FA8094，配色BLACK/WHITE/RED。Pepita 是保时捷具有代表性的经典内饰图案，20 世纪 60 年代初曾作为后期 356 的特别选装，1965 年正式用于初代 911，形成鲜明的跑车内饰风格。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="21" spans="1:17" ht="56" customHeight="1">
       <c r="A21" t="s">
         <v>361</v>
       </c>
@@ -7003,8 +8253,20 @@
       <c r="Q21" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" s="5" t="str">
+        <v>BURGUNDY/WHITE</v>
+      </c>
+      <c r="S21" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料，BURGUNDY/WHITE，编号 FA3018。Pinstripe 以商务西装细条纹为灵感，是 20 世纪 70 年代末至 80 年代保时捷跑车内饰的代表性面料，曾广泛用于风冷 911 G-Model，以及前置发动机车型 924、944 和 928。</v>
+      </c>
+      <c r="T21" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料 FA3018 BURGUNDY/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U21" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料，编号 FA3018，配色BURGUNDY/WHITE。Pinstripe 以商务西装细条纹为灵感，是 20 世纪 70 年代末至 80 年代保时捷跑车内饰的代表性面料，曾广泛用于风冷 911 G-Model，以及前置发动机车型 924、944 和 928。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="22" spans="1:17" ht="56" customHeight="1">
       <c r="A22" t="s">
         <v>366</v>
       </c>
@@ -7032,8 +8294,20 @@
       <c r="Q22" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="23" spans="1:17">
+      <c r="R22" s="5" t="str">
+        <v>MAROON/WHITE</v>
+      </c>
+      <c r="S22" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料，MAROON/WHITE，编号 FA3055。Pinstripe 以商务西装细条纹为灵感，是 20 世纪 70 年代末至 80 年代保时捷跑车内饰的代表性面料，曾广泛用于风冷 911 G-Model，以及前置发动机车型 924、944 和 928。</v>
+      </c>
+      <c r="T22" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料 FA3055 MAROON/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U22" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料，编号 FA3055，配色MAROON/WHITE。Pinstripe 以商务西装细条纹为灵感，是 20 世纪 70 年代末至 80 年代保时捷跑车内饰的代表性面料，曾广泛用于风冷 911 G-Model，以及前置发动机车型 924、944 和 928。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="23" spans="1:17" ht="56" customHeight="1">
       <c r="A23" t="s">
         <v>371</v>
       </c>
@@ -7061,8 +8335,20 @@
       <c r="Q23" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="R23" s="5" t="str">
+        <v>BLACK/DARK GRAY/GRAY</v>
+      </c>
+      <c r="S23" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料，BLACK/DARK GRAY/GRAY，编号 FA3067。Pinstripe 以商务西装细条纹为灵感，是 20 世纪 70 年代末至 80 年代保时捷跑车内饰的代表性面料，曾广泛用于风冷 911 G-Model，以及前置发动机车型 924、944 和 928。</v>
+      </c>
+      <c r="T23" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料 FA3067 BLACK/DARK GRAY/GRAY｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U23" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料，编号 FA3067，配色BLACK/DARK GRAY/GRAY。Pinstripe 以商务西装细条纹为灵感，是 20 世纪 70 年代末至 80 年代保时捷跑车内饰的代表性面料，曾广泛用于风冷 911 G-Model，以及前置发动机车型 924、944 和 928。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="24" spans="1:17" ht="56" customHeight="1">
       <c r="A24" t="s">
         <v>376</v>
       </c>
@@ -7090,8 +8376,20 @@
       <c r="Q24" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" ht="135">
+      <c r="R24" s="5" t="str">
+        <v>BLACK/WHITE</v>
+      </c>
+      <c r="S24" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料，BLACK/WHITE，编号 FA3074。Pinstripe 以商务西装细条纹为灵感，是 20 世纪 70 年代末至 80 年代保时捷跑车内饰的代表性面料，曾广泛用于风冷 911 G-Model，以及前置发动机车型 924、944 和 928。</v>
+      </c>
+      <c r="T24" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料 FA3074 BLACK/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U24" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料，编号 FA3074，配色BLACK/WHITE。Pinstripe 以商务西装细条纹为灵感，是 20 世纪 70 年代末至 80 年代保时捷跑车内饰的代表性面料，曾广泛用于风冷 911 G-Model，以及前置发动机车型 924、944 和 928。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="25" spans="1:17" ht="135">
       <c r="A25" t="s">
         <v>380</v>
       </c>
@@ -7131,8 +8429,20 @@
       <c r="Q25" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="26" spans="1:17">
+      <c r="R25" s="5" t="str">
+        <v>BLUE/BLACK/WHITE/RED</v>
+      </c>
+      <c r="S25" s="5" t="str">
+        <v>Porsche 保时捷格纹复刻面料，BLUE/BLACK/WHITE/RED，编号 FA8525。复古蓝色格纹面料，采用 100% 羊毛和平织斜纹组织。</v>
+      </c>
+      <c r="T25" s="5" t="str">
+        <v>Porsche 保时捷蓝色羊毛格纹面料 FA8525 BLUE/BLACK/WHITE/RED｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U25" s="5" t="str">
+        <v>Porsche 保时捷蓝色羊毛格纹面料，编号 FA8525，配色BLUE/BLACK/WHITE/RED。复古蓝色格纹面料，采用 100% 羊毛和平织斜纹组织。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="26" spans="1:17" ht="56" customHeight="1">
       <c r="A26" t="s">
         <v>385</v>
       </c>
@@ -7160,8 +8470,20 @@
       <c r="Q26" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="27" spans="1:17">
+      <c r="R26" s="5" t="str">
+        <v>GRAY/BLUE</v>
+      </c>
+      <c r="S26" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料，GRAY/BLUE，编号 FA3132。Pinstripe 以商务西装细条纹为灵感，是 20 世纪 70 年代末至 80 年代保时捷跑车内饰的代表性面料，曾广泛用于风冷 911 G-Model，以及前置发动机车型 924、944 和 928。</v>
+      </c>
+      <c r="T26" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料 FA3132 GRAY/BLUE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U26" s="5" t="str">
+        <v>Porsche 保时捷细条纹面料，编号 FA3132，配色GRAY/BLUE。Pinstripe 以商务西装细条纹为灵感，是 20 世纪 70 年代末至 80 年代保时捷跑车内饰的代表性面料，曾广泛用于风冷 911 G-Model，以及前置发动机车型 924、944 和 928。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="27" spans="1:17" ht="56" customHeight="1">
       <c r="A27" t="s">
         <v>390</v>
       </c>
@@ -7189,8 +8511,20 @@
       <c r="Q27" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="R27" s="5" t="str">
+        <v>BLACK/RED</v>
+      </c>
+      <c r="S27" s="5" t="str">
+        <v>Porsche 保时捷绒面细条纹面料，BLACK/RED，编号 FA3217。密实的割绒表面带来近似天鹅绒的柔软、丰厚触感，是 20 世纪 80 年代豪华及商务风格跑车座舱中受到青睐的内饰面料。</v>
+      </c>
+      <c r="T27" s="5" t="str">
+        <v>Porsche 保时捷绒面细条纹面料 FA3217 BLACK/RED｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U27" s="5" t="str">
+        <v>Porsche 保时捷绒面细条纹面料，编号 FA3217，配色BLACK/RED。密实的割绒表面带来近似天鹅绒的柔软、丰厚触感，是 20 世纪 80 年代豪华及商务风格跑车座舱中受到青睐的内饰面料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="28" spans="1:17" ht="56" customHeight="1">
       <c r="A28" t="s">
         <v>395</v>
       </c>
@@ -7218,8 +8552,20 @@
       <c r="Q28" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="29" spans="1:17">
+      <c r="R28" s="5" t="str">
+        <v>BROWN/WHITE</v>
+      </c>
+      <c r="S28" s="5" t="str">
+        <v>Porsche 保时捷绒面细条纹面料，BROWN/WHITE，编号 FA3258。密实的割绒表面带来近似天鹅绒的柔软、丰厚触感，是 20 世纪 80 年代豪华及商务风格跑车座舱中受到青睐的内饰面料。</v>
+      </c>
+      <c r="T28" s="5" t="str">
+        <v>Porsche 保时捷绒面细条纹面料 FA3258 BROWN/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U28" s="5" t="str">
+        <v>Porsche 保时捷绒面细条纹面料，编号 FA3258，配色BROWN/WHITE。密实的割绒表面带来近似天鹅绒的柔软、丰厚触感，是 20 世纪 80 年代豪华及商务风格跑车座舱中受到青睐的内饰面料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="29" spans="1:17" ht="56" customHeight="1">
       <c r="A29" t="s">
         <v>400</v>
       </c>
@@ -7247,8 +8593,20 @@
       <c r="Q29" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="30" spans="1:17">
+      <c r="R29" s="5" t="str">
+        <v>GRAY/WHITE</v>
+      </c>
+      <c r="S29" s="5" t="str">
+        <v>Porsche 保时捷绒面细条纹面料，GRAY/WHITE，编号 FA3272。密实的割绒表面带来近似天鹅绒的柔软、丰厚触感，是 20 世纪 80 年代豪华及商务风格跑车座舱中受到青睐的内饰面料。</v>
+      </c>
+      <c r="T29" s="5" t="str">
+        <v>Porsche 保时捷绒面细条纹面料 FA3272 GRAY/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U29" s="5" t="str">
+        <v>Porsche 保时捷绒面细条纹面料，编号 FA3272，配色GRAY/WHITE。密实的割绒表面带来近似天鹅绒的柔软、丰厚触感，是 20 世纪 80 年代豪华及商务风格跑车座舱中受到青睐的内饰面料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="30" spans="1:17" ht="56" customHeight="1">
       <c r="A30" t="s">
         <v>405</v>
       </c>
@@ -7276,8 +8634,20 @@
       <c r="Q30" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="31" spans="1:17">
+      <c r="R30" s="5" t="str">
+        <v>RED/MAROON</v>
+      </c>
+      <c r="S30" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料，RED/MAROON，编号 FA8118。复刻保时捷标志性的 Studio Check 格纹，适用于 911 Carrera 的 964／993 代车型，以及 928、968 的内饰选材。</v>
+      </c>
+      <c r="T30" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料 FA8118 RED/MAROON｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U30" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料，编号 FA8118，配色RED/MAROON。复刻保时捷标志性的 Studio Check 格纹，适用于 911 Carrera 的 964／993 代车型，以及 928、968 的内饰选材。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="31" spans="1:17" ht="56" customHeight="1">
       <c r="A31" t="s">
         <v>410</v>
       </c>
@@ -7305,8 +8675,20 @@
       <c r="Q31" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="32" spans="1:17">
+      <c r="R31" s="5" t="str">
+        <v>NAVY/BLUE/BLACK</v>
+      </c>
+      <c r="S31" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料，NAVY/BLUE/BLACK，编号 FA8128。复刻保时捷标志性的 Studio Check 格纹，适用于 911 Carrera 的 964／993 代车型，以及 928、968 的内饰选材。</v>
+      </c>
+      <c r="T31" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料 FA8128 NAVY/BLUE/BLACK｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U31" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料，编号 FA8128，配色NAVY/BLUE/BLACK。复刻保时捷标志性的 Studio Check 格纹，适用于 911 Carrera 的 964／993 代车型，以及 928、968 的内饰选材。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="32" spans="1:17" ht="56" customHeight="1">
       <c r="A32" t="s">
         <v>415</v>
       </c>
@@ -7334,8 +8716,20 @@
       <c r="Q32" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="33" spans="1:17">
+      <c r="R32" s="5" t="str">
+        <v>GRAY</v>
+      </c>
+      <c r="S32" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料，GRAY，编号 FA8165。复刻保时捷标志性的 Studio Check 格纹，适用于 911 Carrera 的 964／993 代车型，以及 928、968 的内饰选材。</v>
+      </c>
+      <c r="T32" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料 FA8165 GRAY｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U32" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料，编号 FA8165，配色GRAY。复刻保时捷标志性的 Studio Check 格纹，适用于 911 Carrera 的 964／993 代车型，以及 928、968 的内饰选材。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="33" spans="1:17" ht="56" customHeight="1">
       <c r="A33" t="s">
         <v>420</v>
       </c>
@@ -7363,8 +8757,20 @@
       <c r="Q33" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="34" spans="1:17">
+      <c r="R33" s="5" t="str">
+        <v>GRAY</v>
+      </c>
+      <c r="S33" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料，GRAY，编号 FA8166。复刻保时捷标志性的 Studio Check 格纹，适用于 911 Carrera 的 964／993 代车型，以及 928、968 的内饰选材。</v>
+      </c>
+      <c r="T33" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料 FA8166 GRAY｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U33" s="5" t="str">
+        <v>Porsche 保时捷 Studio Check 复刻面料，编号 FA8166，配色GRAY。复刻保时捷标志性的 Studio Check 格纹，适用于 911 Carrera 的 964／993 代车型，以及 928、968 的内饰选材。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="34" spans="1:17" ht="56" customHeight="1">
       <c r="A34" t="s">
         <v>424</v>
       </c>
@@ -7392,8 +8798,20 @@
       <c r="Q34" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="35" spans="1:17">
+      <c r="R34" s="5" t="str">
+        <v>BLUE/RED/BLACK</v>
+      </c>
+      <c r="S34" s="5" t="str">
+        <v>Porsche 保时捷苏格兰格纹面料，BLUE/RED/BLACK，编号 FA8217。这一经典苏格兰格纹于 1975 年推出，曾是早期 Porsche 保时捷 911 Turbo（930）和 911SC 的知名内饰选装图案。</v>
+      </c>
+      <c r="T34" s="5" t="str">
+        <v>Porsche 保时捷苏格兰格纹面料 FA8217 BLUE/RED/BLACK｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U34" s="5" t="str">
+        <v>Porsche 保时捷苏格兰格纹面料，编号 FA8217，配色BLUE/RED/BLACK。这一经典苏格兰格纹于 1975 年推出，曾是早期 Porsche 保时捷 911 Turbo（930）和 911SC 的知名内饰选装图案。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="35" spans="1:17" ht="56" customHeight="1">
       <c r="A35" t="s">
         <v>429</v>
       </c>
@@ -7421,8 +8839,20 @@
       <c r="Q35" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="36" spans="1:17">
+      <c r="R35" s="5" t="str">
+        <v>NAVY/BLUE/BLACK</v>
+      </c>
+      <c r="S35" s="5" t="str">
+        <v>Porsche 保时捷苏格兰格纹面料，NAVY/BLUE/BLACK，编号 FA8237。这一经典苏格兰格纹于 1975 年推出，曾是早期 Porsche 保时捷 911 Turbo（930）和 911SC 的知名内饰选装图案。</v>
+      </c>
+      <c r="T35" s="5" t="str">
+        <v>Porsche 保时捷苏格兰格纹面料 FA8237 NAVY/BLUE/BLACK｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U35" s="5" t="str">
+        <v>Porsche 保时捷苏格兰格纹面料，编号 FA8237，配色NAVY/BLUE/BLACK。这一经典苏格兰格纹于 1975 年推出，曾是早期 Porsche 保时捷 911 Turbo（930）和 911SC 的知名内饰选装图案。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="36" spans="1:17" ht="56" customHeight="1">
       <c r="A36" t="s">
         <v>433</v>
       </c>
@@ -7450,8 +8880,20 @@
       <c r="Q36" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" ht="240" customHeight="1">
+      <c r="R36" s="5" t="str">
+        <v>GRAY/BLUE/WHITE</v>
+      </c>
+      <c r="S36" s="5" t="str">
+        <v>Porsche 保时捷苏格兰格纹面料，GRAY/BLUE/WHITE，编号 FA8271。这一经典苏格兰格纹于 1975 年推出，曾是早期 Porsche 保时捷 911 Turbo（930）和 911SC 的知名内饰选装图案。</v>
+      </c>
+      <c r="T36" s="5" t="str">
+        <v>Porsche 保时捷苏格兰格纹面料 FA8271 GRAY/BLUE/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U36" s="5" t="str">
+        <v>Porsche 保时捷苏格兰格纹面料，编号 FA8271，配色GRAY/BLUE/WHITE。这一经典苏格兰格纹于 1975 年推出，曾是早期 Porsche 保时捷 911 Turbo（930）和 911SC 的知名内饰选装图案。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="37" spans="1:17" ht="240" customHeight="1">
       <c r="A37" t="s">
         <v>438</v>
       </c>
@@ -7488,8 +8930,20 @@
       <c r="Q37" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" ht="120" customHeight="1">
+      <c r="R37" s="5" t="str">
+        <v>BLACK/RED/BLUE</v>
+      </c>
+      <c r="S37" s="5" t="str">
+        <v>精选汽车座椅格纹面料，BLACK/RED/BLUE，编号 FA8517。带泡棉背衬的汽车座椅面料，以保时捷 Sonderwunsch 项目的历史内饰为灵感，采用红、蓝、黑格纹，呼应 992 代 911 Turbo Sonderwunsch 及 1974 年“Louise”Turbo No. 1 的座舱风格。</v>
+      </c>
+      <c r="T37" s="5" t="str">
+        <v>Porsche 保时捷 Sonderwunsch 风格格纹面料 FA8517 BLACK/RED/BLUE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U37" s="5" t="str">
+        <v>Porsche 保时捷 Sonderwunsch 风格格纹面料，编号 FA8517，配色BLACK/RED/BLUE。带泡棉背衬的汽车座椅面料，以保时捷 Sonderwunsch 项目的历史内饰为灵感，采用红、蓝、黑格纹，呼应 992 代 911 Turbo Sonderwunsch 及 1974 年“Louise”Turbo No. 1 的座舱风格。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="38" spans="1:17" ht="120" customHeight="1">
       <c r="A38" t="s">
         <v>446</v>
       </c>
@@ -7526,8 +8980,20 @@
       <c r="Q38" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" ht="210" customHeight="1">
+      <c r="R38" s="5" t="str">
+        <v>BLUE/NAVY/ORANGE</v>
+      </c>
+      <c r="S38" s="5" t="str">
+        <v>精选汽车座椅格纹面料，BLUE/NAVY/ORANGE，编号 FA8553。复刻 20 世纪 70 年代末至 80 年代 Ford 福特 Capri S（Mk2／Mk3）的 Carla 格纹内饰面料。</v>
+      </c>
+      <c r="T38" s="5" t="str">
+        <v>Ford 福特 Capri S Carla 格纹复刻面料 FA8553 BLUE/NAVY/ORANGE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U38" s="5" t="str">
+        <v>Ford 福特 Capri S Carla 格纹复刻面料，编号 FA8553，配色BLUE/NAVY/ORANGE。复刻 20 世纪 70 年代末至 80 年代 Ford 福特 Capri S（Mk2／Mk3）的 Carla 格纹内饰面料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="39" spans="1:17" ht="210" customHeight="1">
       <c r="A39" t="s">
         <v>454</v>
       </c>
@@ -7564,8 +9030,20 @@
       <c r="Q39" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" ht="105" customHeight="1">
+      <c r="R39" s="5" t="str">
+        <v>GRAY/BLUE</v>
+      </c>
+      <c r="S39" s="5" t="str">
+        <v>精选汽车座椅格纹面料，GRAY/BLUE，编号 FA8075。复刻 20 世纪 70 年代末至 80 年代墨西哥普埃布拉工厂生产的大众甲壳虫内饰面料，呈现原有座椅织物纹理。</v>
+      </c>
+      <c r="T39" s="5" t="str">
+        <v>Volkswagen 大众甲壳虫内饰复刻面料 FA8075 GRAY/BLUE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U39" s="5" t="str">
+        <v>Volkswagen 大众甲壳虫内饰复刻面料，编号 FA8075，配色GRAY/BLUE。复刻 20 世纪 70 年代末至 80 年代墨西哥普埃布拉工厂生产的大众甲壳虫内饰面料，呈现原有座椅织物纹理。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="40" spans="1:17" ht="105" customHeight="1">
       <c r="A40" t="s">
         <v>461</v>
       </c>
@@ -7602,8 +9080,20 @@
       <c r="Q40" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="41" spans="1:17">
+      <c r="R40" s="5" t="str">
+        <v>BLACK/WHITE</v>
+      </c>
+      <c r="S40" s="5" t="str">
+        <v>精选汽车座椅格纹面料，BLACK/WHITE，编号 FA8072。Satellite Grey 内饰面料，用于第三代 MINI Cooper（F56）的座椅及门板修复选材。</v>
+      </c>
+      <c r="T40" s="5" t="str">
+        <v>MINI Cooper F56 Satellite Grey 内饰面料 FA8072 BLACK/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U40" s="5" t="str">
+        <v>MINI Cooper F56 Satellite Grey 内饰面料，编号 FA8072，配色BLACK/WHITE。Satellite Grey 内饰面料，用于第三代 MINI Cooper（F56）的座椅及门板修复选材。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="41" spans="1:17" ht="72" customHeight="1">
       <c r="A41" t="s">
         <v>468</v>
       </c>
@@ -7631,8 +9121,20 @@
       <c r="Q41" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="42" spans="1:17">
+      <c r="R41" s="5" t="str">
+        <v>BLUE/NAVY/RED</v>
+      </c>
+      <c r="S41" s="5" t="str">
+        <v>Spirit of Le Mans 勒芒风格羊毛格纹面料，BLUE/NAVY/RED，编号 FA2002。Spirit of Le Mans（SOLM）羊毛系列以赛车运动为灵感，在苏格兰织造，专为高品质汽车内饰设计。采用 100% 羊毛与耐用的 2/2 斜纹组织，每延米重 500 克（365 克／平方米），并预先施加针对汽车安全要求的防污及阻燃处理。</v>
+      </c>
+      <c r="T41" s="5" t="str">
+        <v>Spirit of Le Mans 勒芒风格羊毛格纹面料 FA2002 BLUE/NAVY/RED｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U41" s="5" t="str">
+        <v>Spirit of Le Mans 勒芒风格羊毛格纹面料，编号 FA2002，配色BLUE/NAVY/RED。Spirit of Le Mans（SOLM）羊毛系列以赛车运动为灵感，在苏格兰织造，专为高品质汽车内饰设计。采用 100% 羊毛与耐用的 2/2 斜纹组织，每延米重 500 克（365 克／平方米），并预先施加针对汽车安全要求的防污及阻燃处理。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="42" spans="1:17" ht="72" customHeight="1">
       <c r="A42" t="s">
         <v>473</v>
       </c>
@@ -7660,8 +9162,20 @@
       <c r="Q42" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="43" spans="1:17">
+      <c r="R42" s="5" t="str">
+        <v>BLUE/ORANGE/NAVY</v>
+      </c>
+      <c r="S42" s="5" t="str">
+        <v>Spirit of Le Mans 勒芒风格羊毛格纹面料，BLUE/ORANGE/NAVY，编号 FA2202。Spirit of Le Mans（SOLM）羊毛系列以赛车运动为灵感，在苏格兰织造，专为高品质汽车内饰设计。采用 100% 羊毛与耐用的 2/2 斜纹组织，每延米重 500 克（365 克／平方米），并预先施加针对汽车安全要求的防污及阻燃处理。</v>
+      </c>
+      <c r="T42" s="5" t="str">
+        <v>Spirit of Le Mans 勒芒风格羊毛格纹面料 FA2202 BLUE/ORANGE/NAVY｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U42" s="5" t="str">
+        <v>Spirit of Le Mans 勒芒风格羊毛格纹面料，编号 FA2202，配色BLUE/ORANGE/NAVY。Spirit of Le Mans（SOLM）羊毛系列以赛车运动为灵感，在苏格兰织造，专为高品质汽车内饰设计。采用 100% 羊毛与耐用的 2/2 斜纹组织，每延米重 500 克（365 克／平方米），并预先施加针对汽车安全要求的防污及阻燃处理。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="43" spans="1:17" ht="72" customHeight="1">
       <c r="A43" t="s">
         <v>478</v>
       </c>
@@ -7689,8 +9203,20 @@
       <c r="Q43" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" ht="15" customHeight="1">
+      <c r="R43" s="5" t="str">
+        <v>BLUE/BLACK/RED</v>
+      </c>
+      <c r="S43" s="5" t="str">
+        <v>Spirit of Le Mans 勒芒风格羊毛格纹面料，BLUE/BLACK/RED，编号 FA2729。Spirit of Le Mans（SOLM）羊毛系列以赛车运动为灵感，在苏格兰织造，专为高品质汽车内饰设计。采用 100% 羊毛与耐用的 2/2 斜纹组织，每延米重 500 克（365 克／平方米），并预先施加针对汽车安全要求的防污及阻燃处理。</v>
+      </c>
+      <c r="T43" s="5" t="str">
+        <v>Spirit of Le Mans 勒芒风格羊毛格纹面料 FA2729 BLUE/BLACK/RED｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U43" s="5" t="str">
+        <v>Spirit of Le Mans 勒芒风格羊毛格纹面料，编号 FA2729，配色BLUE/BLACK/RED。Spirit of Le Mans（SOLM）羊毛系列以赛车运动为灵感，在苏格兰织造，专为高品质汽车内饰设计。采用 100% 羊毛与耐用的 2/2 斜纹组织，每延米重 500 克（365 克／平方米），并预先施加针对汽车安全要求的防污及阻燃处理。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="44" spans="1:17" ht="72" customHeight="1">
       <c r="A44" t="s">
         <v>483</v>
       </c>
@@ -7718,8 +9244,20 @@
       <c r="Q44" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" ht="15" customHeight="1">
+      <c r="R44" s="5" t="str">
+        <v>DARK GRAY</v>
+      </c>
+      <c r="S44" s="5" t="str">
+        <v>BMW 宝马千鸟格复刻面料，DARK GRAY，编号 FA1817。德国复刻千鸟格（Pepita）座椅面料采用耐用的羊毛混纺结构，为经典 BMW 宝马 E10（2002）、E21、E28（5 系）及 E30（3 系，包括 325i 和早期 M3）提供接近原有风格的纹理与饰面，适合座椅中央拼片、门板和内饰修复。</v>
+      </c>
+      <c r="T44" s="5" t="str">
+        <v>BMW 宝马千鸟格复刻面料 FA1817 DARK GRAY｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U44" s="5" t="str">
+        <v>BMW 宝马千鸟格复刻面料，编号 FA1817，配色DARK GRAY。德国复刻千鸟格（Pepita）座椅面料采用耐用的羊毛混纺结构，为经典 BMW 宝马 E10（2002）、E21、E28（5 系）及 E30（3 系，包括 325i 和早期 M3）提供接近原有风格的纹理与饰面，适合座椅中央拼片、门板和内饰修复。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="45" spans="1:17" ht="72" customHeight="1">
       <c r="A45" t="s">
         <v>488</v>
       </c>
@@ -7747,8 +9285,20 @@
       <c r="Q45" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" ht="15" customHeight="1">
+      <c r="R45" s="5" t="str">
+        <v>LIGHT GRAY</v>
+      </c>
+      <c r="S45" s="5" t="str">
+        <v>BMW 宝马千鸟格复刻面料，LIGHT GRAY，编号 FA1815。德国复刻千鸟格（Pepita）座椅面料采用耐用的羊毛混纺结构，为经典 BMW 宝马 E10（2002）、E21、E28（5 系）及 E30（3 系，包括 325i 和早期 M3）提供接近原有风格的纹理与饰面，适合座椅中央拼片、门板和内饰修复。</v>
+      </c>
+      <c r="T45" s="5" t="str">
+        <v>BMW 宝马千鸟格复刻面料 FA1815 LIGHT GRAY｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U45" s="5" t="str">
+        <v>BMW 宝马千鸟格复刻面料，编号 FA1815，配色LIGHT GRAY。德国复刻千鸟格（Pepita）座椅面料采用耐用的羊毛混纺结构，为经典 BMW 宝马 E10（2002）、E21、E28（5 系）及 E30（3 系，包括 325i 和早期 M3）提供接近原有风格的纹理与饰面，适合座椅中央拼片、门板和内饰修复。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="46" spans="1:17" ht="40" customHeight="1">
       <c r="A46" t="s">
         <v>493</v>
       </c>
@@ -7776,8 +9326,20 @@
       <c r="Q46" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" ht="15" customHeight="1">
+      <c r="R46" s="5" t="str">
+        <v>BROWN/WHITE</v>
+      </c>
+      <c r="S46" s="5" t="str">
+        <v>BMW 宝马 ÜBERKARO 格纹复刻面料，BROWN/WHITE，编号 FA8275。BMW ÜBERKARO 是经典苏格兰格纹，因用于宝马 E30 及稀有的 M3 Evolution II 车型而闻名。</v>
+      </c>
+      <c r="T46" s="5" t="str">
+        <v>BMW 宝马 ÜBERKARO 格纹复刻面料 FA8275 BROWN/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U46" s="5" t="str">
+        <v>BMW 宝马 ÜBERKARO 格纹复刻面料，编号 FA8275，配色BROWN/WHITE。BMW ÜBERKARO 是经典苏格兰格纹，因用于宝马 E30 及稀有的 M3 Evolution II 车型而闻名。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="47" spans="1:17" ht="40" customHeight="1">
       <c r="A47" t="s">
         <v>497</v>
       </c>
@@ -7805,8 +9367,20 @@
       <c r="Q47" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" ht="30" customHeight="1">
+      <c r="R47" s="5" t="str">
+        <v>BLACK/WHITE</v>
+      </c>
+      <c r="S47" s="5" t="str">
+        <v>BMW 宝马 ÜBERKARO 格纹复刻面料，BLACK/WHITE，编号 FA9368。BMW ÜBERKARO 是经典苏格兰格纹，因用于宝马 E30 及稀有的 M3 Evolution II 车型而闻名。</v>
+      </c>
+      <c r="T47" s="5" t="str">
+        <v>BMW 宝马 ÜBERKARO 格纹复刻面料 FA9368 BLACK/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U47" s="5" t="str">
+        <v>BMW 宝马 ÜBERKARO 格纹复刻面料，编号 FA9368，配色BLACK/WHITE。BMW ÜBERKARO 是经典苏格兰格纹，因用于宝马 E30 及稀有的 M3 Evolution II 车型而闻名。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="48" spans="1:17" ht="56" customHeight="1">
       <c r="A48" t="s">
         <v>501</v>
       </c>
@@ -7834,8 +9408,20 @@
       <c r="Q48" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" ht="30" customHeight="1">
+      <c r="R48" s="5" t="str">
+        <v>BLUE/WHITE</v>
+      </c>
+      <c r="S48" s="5" t="str">
+        <v>Mercedes-Benz 奔驰千鸟格复刻面料，BLUE/WHITE，编号 FA8024。这款双色千鸟格面料参照 20 世纪 60 年代初奔驰中型车的原有规格织造，适用于 W110“尾鳍”轿车的内饰修复，包括 190c、190Dc 和早期 220 车型。</v>
+      </c>
+      <c r="T48" s="5" t="str">
+        <v>Mercedes-Benz 奔驰千鸟格复刻面料 FA8024 BLUE/WHITE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U48" s="5" t="str">
+        <v>Mercedes-Benz 奔驰千鸟格复刻面料，编号 FA8024，配色BLUE/WHITE。这款双色千鸟格面料参照 20 世纪 60 年代初奔驰中型车的原有规格织造，适用于 W110“尾鳍”轿车的内饰修复，包括 190c、190Dc 和早期 220 车型。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="49" spans="1:17" ht="56" customHeight="1">
       <c r="A49" t="s">
         <v>505</v>
       </c>
@@ -7863,8 +9449,20 @@
       <c r="Q49" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" ht="15" customHeight="1">
+      <c r="R49" s="5" t="str">
+        <v>BLACK/BEIGE</v>
+      </c>
+      <c r="S49" s="5" t="str">
+        <v>Mercedes-Benz 奔驰千鸟格复刻面料，BLACK/BEIGE，编号 FA8066。这款双色千鸟格面料参照 20 世纪 60 年代初奔驰中型车的原有规格织造，适用于 W110“尾鳍”轿车的内饰修复，包括 190c、190Dc 和早期 220 车型。</v>
+      </c>
+      <c r="T49" s="5" t="str">
+        <v>Mercedes-Benz 奔驰千鸟格复刻面料 FA8066 BLACK/BEIGE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U49" s="5" t="str">
+        <v>Mercedes-Benz 奔驰千鸟格复刻面料，编号 FA8066，配色BLACK/BEIGE。这款双色千鸟格面料参照 20 世纪 60 年代初奔驰中型车的原有规格织造，适用于 W110“尾鳍”轿车的内饰修复，包括 190c、190Dc 和早期 220 车型。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="50" spans="1:17" ht="56" customHeight="1">
       <c r="A50" t="s">
         <v>510</v>
       </c>
@@ -7892,8 +9490,20 @@
       <c r="Q50" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" ht="15" customHeight="1">
+      <c r="R50" s="5" t="str">
+        <v>ORAGNE/YELLOW</v>
+      </c>
+      <c r="S50" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料，ORAGNE/YELLOW，编号 FA8715。参照 1968—1979 年 Volkswagen 大众 Type 2 Westfalia 露营车原有规格制作的内饰复刻面料，以厚实、密实的织法呈现经典方格图案。</v>
+      </c>
+      <c r="T50" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料 FA8715 ORAGNE/YELLOW｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U50" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料，编号 FA8715，配色ORAGNE/YELLOW。参照 1968—1979 年 Volkswagen 大众 Type 2 Westfalia 露营车原有规格制作的内饰复刻面料，以厚实、密实的织法呈现经典方格图案。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="51" spans="1:17" ht="56" customHeight="1">
       <c r="A51" t="s">
         <v>515</v>
       </c>
@@ -7921,8 +9531,20 @@
       <c r="Q51" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" ht="15" customHeight="1">
+      <c r="R51" s="5" t="str">
+        <v>BLUE/GREEN</v>
+      </c>
+      <c r="S51" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料，BLUE/GREEN，编号 FA8726。参照 1968—1979 年 Volkswagen 大众 Type 2 Westfalia 露营车原有规格制作的内饰复刻面料，以厚实、密实的织法呈现经典方格图案。</v>
+      </c>
+      <c r="T51" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料 FA8726 BLUE/GREEN｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U51" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料，编号 FA8726，配色BLUE/GREEN。参照 1968—1979 年 Volkswagen 大众 Type 2 Westfalia 露营车原有规格制作的内饰复刻面料，以厚实、密实的织法呈现经典方格图案。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="52" spans="1:17" ht="56" customHeight="1">
       <c r="A52" t="s">
         <v>520</v>
       </c>
@@ -7950,8 +9572,20 @@
       <c r="Q52" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" ht="15" customHeight="1">
+      <c r="R52" s="5" t="str">
+        <v>GREEN/YELLOW</v>
+      </c>
+      <c r="S52" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料，GREEN/YELLOW，编号 FA8734。参照 1968—1979 年 Volkswagen 大众 Type 2 Westfalia 露营车原有规格制作的内饰复刻面料，以厚实、密实的织法呈现经典方格图案。</v>
+      </c>
+      <c r="T52" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料 FA8734 GREEN/YELLOW｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U52" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料，编号 FA8734，配色GREEN/YELLOW。参照 1968—1979 年 Volkswagen 大众 Type 2 Westfalia 露营车原有规格制作的内饰复刻面料，以厚实、密实的织法呈现经典方格图案。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="53" spans="1:17" ht="56" customHeight="1">
       <c r="A53" t="s">
         <v>525</v>
       </c>
@@ -7979,8 +9613,20 @@
       <c r="Q53" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" ht="90" customHeight="1">
+      <c r="R53" s="5" t="str">
+        <v>BROWN/BEIGE</v>
+      </c>
+      <c r="S53" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料，BROWN/BEIGE，编号 FA8754。参照 1968—1979 年 Volkswagen 大众 Type 2 Westfalia 露营车原有规格制作的内饰复刻面料，以厚实、密实的织法呈现经典方格图案。</v>
+      </c>
+      <c r="T53" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料 FA8754 BROWN/BEIGE｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U53" s="5" t="str">
+        <v>Volkswagen 大众 T2 格纹复刻面料，编号 FA8754，配色BROWN/BEIGE。参照 1968—1979 年 Volkswagen 大众 Type 2 Westfalia 露营车原有规格制作的内饰复刻面料，以厚实、密实的织法呈现经典方格图案。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="54" spans="1:17" ht="90" customHeight="1">
       <c r="A54" t="s">
         <v>629</v>
       </c>
@@ -8023,8 +9669,20 @@
       <c r="Q54" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" ht="75" customHeight="1">
+      <c r="R54" s="5" t="str">
+        <v>FA1228</v>
+      </c>
+      <c r="S54" s="5" t="str">
+        <v>Ferrari 法拉利技术面料，编号 FA1228。面向性能导向汽车内饰的法拉利技术面料。</v>
+      </c>
+      <c r="T54" s="5" t="str">
+        <v>Ferrari 法拉利技术面料 FA1228｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U54" s="5" t="str">
+        <v>Ferrari 法拉利技术面料，编号 FA1228。面向性能导向汽车内饰的法拉利技术面料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="55" spans="1:17" ht="75" customHeight="1">
       <c r="A55" t="s">
         <v>630</v>
       </c>
@@ -8067,8 +9725,20 @@
       <c r="Q55" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="56" spans="1:17" ht="15">
+      <c r="R55" s="5" t="str">
+        <v>FA1269</v>
+      </c>
+      <c r="S55" s="5" t="str">
+        <v>Ferrari 法拉利技术面料，编号 FA1269。面向性能导向汽车内饰的法拉利技术面料。</v>
+      </c>
+      <c r="T55" s="5" t="str">
+        <v>Ferrari 法拉利技术面料 FA1269｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U55" s="5" t="str">
+        <v>Ferrari 法拉利技术面料，编号 FA1269。面向性能导向汽车内饰的法拉利技术面料。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="56" spans="1:17" ht="56" customHeight="1">
       <c r="A56" t="s">
         <v>546</v>
       </c>
@@ -8099,8 +9769,20 @@
       <c r="Q56" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="57" spans="1:17" ht="15">
+      <c r="R56" s="5" t="str">
+        <v>FA1869</v>
+      </c>
+      <c r="S56" s="5" t="str">
+        <v>3D 立体间隔汽车面料，编号 FA1869。采用 3D 针织间隔结构的高性能技术面料，主要用于赛道取向车型及现代公路车型的座椅拼片、门板内衬和轻量化碳纤维赛车桶椅。</v>
+      </c>
+      <c r="T56" s="5" t="str">
+        <v>3D 立体间隔汽车面料 FA1869｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U56" s="5" t="str">
+        <v>3D 立体间隔汽车面料，编号 FA1869。采用 3D 针织间隔结构的高性能技术面料，主要用于赛道取向车型及现代公路车型的座椅拼片、门板内衬和轻量化碳纤维赛车桶椅。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="57" spans="1:17" ht="56" customHeight="1">
       <c r="A57" t="s">
         <v>548</v>
       </c>
@@ -8131,8 +9813,20 @@
       <c r="Q57" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="58" spans="1:17" ht="15">
+      <c r="R57" s="5" t="str">
+        <v>FA6107</v>
+      </c>
+      <c r="S57" s="5" t="str">
+        <v>SuperFabric 高耐磨复合面料，编号 FA6107。SuperFabric® 是高性能复合材料，在保留常规织物柔韧性、透气性及重量特点的同时，提供较高的耐磨、耐切割、耐划割及耐穿刺性能。</v>
+      </c>
+      <c r="T57" s="5" t="str">
+        <v>SuperFabric 高耐磨复合面料 FA6107｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U57" s="5" t="str">
+        <v>SuperFabric 高耐磨复合面料，编号 FA6107。SuperFabric® 是高性能复合材料，在保留常规织物柔韧性、透气性及重量特点的同时，提供较高的耐磨、耐切割、耐划割及耐穿刺性能。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="58" spans="1:17" ht="40" customHeight="1">
       <c r="A58" t="s">
         <v>550</v>
       </c>
@@ -8180,6 +9874,18 @@
       </c>
       <c r="Q58" t="s">
         <v>658</v>
+      </c>
+      <c r="R58" s="5" t="str">
+        <v>FA8526</v>
+      </c>
+      <c r="S58" s="5" t="str">
+        <v>Porsche 保时捷格纹复刻面料，编号 FA8526。复刻 Porsche 保时捷 914 Ski-Blue 蓝色苏格兰格纹内饰面料，材质为聚酯纤维。</v>
+      </c>
+      <c r="T58" s="5" t="str">
+        <v>Porsche 保时捷 914 聚酯纤维格纹面料 FA8526｜CAMARI 卡玛瑞</v>
+      </c>
+      <c r="U58" s="5" t="str">
+        <v>Porsche 保时捷 914 聚酯纤维格纹面料，编号 FA8526。复刻 Porsche 保时捷 914 Ski-Blue 蓝色苏格兰格纹内饰面料，材质为聚酯纤维。 查看 CAMARI 卡玛瑞的面料规格与色样。</v>
       </c>
     </row>
   </sheetData>
@@ -8190,10 +9896,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <col min="7" max="7" width="48" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="70" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1" spans="1:6">
       <c r="A1" t="s">
         <v>260</v>
       </c>
@@ -8212,8 +9922,14 @@
       <c r="F1" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="2">
+      <c r="G1" s="0" t="str">
+        <v>label_zh</v>
+      </c>
+      <c r="H1" s="0" t="str">
+        <v>value_zh</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="2" ht="24" customHeight="1">
       <c r="A2" t="str">
         <v>fa8526</v>
       </c>
@@ -8231,6 +9947,12 @@
       </c>
       <c r="F2" t="str">
         <v>ポリエステル</v>
+      </c>
+      <c r="G2" s="5" t="str">
+        <v>材质</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <v>聚酯纤维</v>
       </c>
     </row>
   </sheetData>
@@ -8241,10 +9963,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <col min="9" max="9" width="70" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="95" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8268,6 +9994,12 @@
       </c>
       <c r="H1" t="s">
         <v>555</v>
+      </c>
+      <c r="I1" s="0" t="str">
+        <v>title_zh</v>
+      </c>
+      <c r="J1" s="0" t="str">
+        <v>description_zh</v>
       </c>
     </row>
   </sheetData>
@@ -8278,13 +10010,14 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
+  <cols xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="70" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1" spans="1:5">
       <c r="A1" t="s">
         <v>260</v>
       </c>
@@ -8300,8 +10033,11 @@
       <c r="E1" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="0" t="str">
+        <v>alt_zh</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="2" spans="1:5" ht="24" customHeight="1">
       <c r="A2" t="s">
         <v>268</v>
       </c>
@@ -8311,8 +10047,9 @@
       <c r="C2" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="3" spans="1:5" ht="24" customHeight="1">
       <c r="A3" t="s">
         <v>273</v>
       </c>
@@ -8322,8 +10059,9 @@
       <c r="C3" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="4" spans="1:5" ht="24" customHeight="1">
       <c r="A4" t="s">
         <v>278</v>
       </c>
@@ -8333,8 +10071,9 @@
       <c r="C4" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="5" spans="1:5" ht="24" customHeight="1">
       <c r="A5" t="s">
         <v>283</v>
       </c>
@@ -8344,8 +10083,9 @@
       <c r="C5" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="6" spans="1:5" ht="24" customHeight="1">
       <c r="A6" t="s">
         <v>288</v>
       </c>
@@ -8355,8 +10095,9 @@
       <c r="C6" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="7" spans="1:5" ht="24" customHeight="1">
       <c r="A7" t="s">
         <v>293</v>
       </c>
@@ -8366,8 +10107,9 @@
       <c r="C7" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="8" spans="1:5" ht="24" customHeight="1">
       <c r="A8" t="s">
         <v>298</v>
       </c>
@@ -8377,8 +10119,9 @@
       <c r="C8" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="9" spans="1:5" ht="24" customHeight="1">
       <c r="A9" t="s">
         <v>303</v>
       </c>
@@ -8388,8 +10131,9 @@
       <c r="C9" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="10" spans="1:5" ht="24" customHeight="1">
       <c r="A10" t="s">
         <v>308</v>
       </c>
@@ -8399,8 +10143,9 @@
       <c r="C10" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="11" spans="1:5" ht="24" customHeight="1">
       <c r="A11" t="s">
         <v>313</v>
       </c>
@@ -8410,8 +10155,9 @@
       <c r="C11" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="12" spans="1:5" ht="24" customHeight="1">
       <c r="A12" t="s">
         <v>318</v>
       </c>
@@ -8421,8 +10167,9 @@
       <c r="C12" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="13" spans="1:5" ht="24" customHeight="1">
       <c r="A13" t="s">
         <v>323</v>
       </c>
@@ -8432,8 +10179,9 @@
       <c r="C13" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="14" spans="1:5" ht="24" customHeight="1">
       <c r="A14" t="s">
         <v>328</v>
       </c>
@@ -8443,8 +10191,9 @@
       <c r="C14" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="15" spans="1:5" ht="24" customHeight="1">
       <c r="A15" t="s">
         <v>333</v>
       </c>
@@ -8454,8 +10203,9 @@
       <c r="C15" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="16" spans="1:5" ht="24" customHeight="1">
       <c r="A16" t="s">
         <v>338</v>
       </c>
@@ -8465,8 +10215,9 @@
       <c r="C16" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="F16" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="17" spans="1:3" ht="24" customHeight="1">
       <c r="A17" t="s">
         <v>343</v>
       </c>
@@ -8476,8 +10227,9 @@
       <c r="C17" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="F17" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="18" spans="1:3" ht="24" customHeight="1">
       <c r="A18" t="s">
         <v>347</v>
       </c>
@@ -8487,8 +10239,9 @@
       <c r="C18" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="F18" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="19" spans="1:3" ht="24" customHeight="1">
       <c r="A19" t="s">
         <v>352</v>
       </c>
@@ -8498,8 +10251,9 @@
       <c r="C19" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="F19" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="20" spans="1:3" ht="24" customHeight="1">
       <c r="A20" t="s">
         <v>357</v>
       </c>
@@ -8509,8 +10263,9 @@
       <c r="C20" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="F20" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="21" spans="1:3" ht="24" customHeight="1">
       <c r="A21" t="s">
         <v>361</v>
       </c>
@@ -8520,8 +10275,9 @@
       <c r="C21" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="F21" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="22" spans="1:3" ht="24" customHeight="1">
       <c r="A22" t="s">
         <v>366</v>
       </c>
@@ -8531,8 +10287,9 @@
       <c r="C22" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="F22" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="23" spans="1:3" ht="24" customHeight="1">
       <c r="A23" t="s">
         <v>371</v>
       </c>
@@ -8542,8 +10299,9 @@
       <c r="C23" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="F23" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="24" spans="1:3" ht="24" customHeight="1">
       <c r="A24" t="s">
         <v>376</v>
       </c>
@@ -8553,8 +10311,9 @@
       <c r="C24" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="F24" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="25" spans="1:3" ht="24" customHeight="1">
       <c r="A25" t="s">
         <v>380</v>
       </c>
@@ -8564,8 +10323,9 @@
       <c r="C25" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="F25" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="26" spans="1:3" ht="24" customHeight="1">
       <c r="A26" t="s">
         <v>385</v>
       </c>
@@ -8575,8 +10335,9 @@
       <c r="C26" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="F26" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="27" spans="1:3" ht="24" customHeight="1">
       <c r="A27" t="s">
         <v>390</v>
       </c>
@@ -8586,8 +10347,9 @@
       <c r="C27" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="F27" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="28" spans="1:3" ht="24" customHeight="1">
       <c r="A28" t="s">
         <v>395</v>
       </c>
@@ -8597,8 +10359,9 @@
       <c r="C28" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="F28" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="29" spans="1:3" ht="24" customHeight="1">
       <c r="A29" t="s">
         <v>400</v>
       </c>
@@ -8608,8 +10371,9 @@
       <c r="C29" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="F29" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="30" spans="1:3" ht="24" customHeight="1">
       <c r="A30" t="s">
         <v>405</v>
       </c>
@@ -8619,8 +10383,9 @@
       <c r="C30" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="F30" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="31" spans="1:3" ht="24" customHeight="1">
       <c r="A31" t="s">
         <v>410</v>
       </c>
@@ -8630,8 +10395,9 @@
       <c r="C31" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="F31" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="32" spans="1:3" ht="24" customHeight="1">
       <c r="A32" t="s">
         <v>415</v>
       </c>
@@ -8641,8 +10407,9 @@
       <c r="C32" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="F32" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="33" spans="1:3" ht="24" customHeight="1">
       <c r="A33" t="s">
         <v>420</v>
       </c>
@@ -8652,8 +10419,9 @@
       <c r="C33" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="F33" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="34" spans="1:3" ht="24" customHeight="1">
       <c r="A34" t="s">
         <v>424</v>
       </c>
@@ -8663,8 +10431,9 @@
       <c r="C34" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="F34" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="35" spans="1:3" ht="24" customHeight="1">
       <c r="A35" t="s">
         <v>429</v>
       </c>
@@ -8674,8 +10443,9 @@
       <c r="C35" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="F35" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="36" spans="1:3" ht="24" customHeight="1">
       <c r="A36" t="s">
         <v>433</v>
       </c>
@@ -8685,8 +10455,9 @@
       <c r="C36" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="F36" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="37" spans="1:3" ht="24" customHeight="1">
       <c r="A37" t="s">
         <v>438</v>
       </c>
@@ -8696,8 +10467,9 @@
       <c r="C37" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="F37" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="38" spans="1:3" ht="24" customHeight="1">
       <c r="A38" t="s">
         <v>446</v>
       </c>
@@ -8707,8 +10479,9 @@
       <c r="C38" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="F38" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="39" spans="1:3" ht="24" customHeight="1">
       <c r="A39" t="s">
         <v>468</v>
       </c>
@@ -8718,8 +10491,9 @@
       <c r="C39" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="F39" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="40" spans="1:3" ht="24" customHeight="1">
       <c r="A40" t="s">
         <v>473</v>
       </c>
@@ -8729,8 +10503,9 @@
       <c r="C40" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="F40" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="41" spans="1:3" ht="24" customHeight="1">
       <c r="A41" t="s">
         <v>478</v>
       </c>
@@ -8740,8 +10515,9 @@
       <c r="C41" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="F41" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="42" spans="1:3" ht="24" customHeight="1">
       <c r="A42" t="s">
         <v>468</v>
       </c>
@@ -8751,8 +10527,9 @@
       <c r="C42" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="F42" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="43" spans="1:3" ht="24" customHeight="1">
       <c r="A43" t="s">
         <v>473</v>
       </c>
@@ -8762,8 +10539,9 @@
       <c r="C43" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="F43" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="44" spans="1:3" ht="24" customHeight="1">
       <c r="A44" t="s">
         <v>478</v>
       </c>
@@ -8773,8 +10551,9 @@
       <c r="C44" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="F44" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="45" spans="1:3" ht="24" customHeight="1">
       <c r="A45" t="s">
         <v>478</v>
       </c>
@@ -8784,8 +10563,9 @@
       <c r="C45" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="F45" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="46" spans="1:3" ht="24" customHeight="1">
       <c r="A46" t="s">
         <v>478</v>
       </c>
@@ -8795,8 +10575,9 @@
       <c r="C46" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="F46" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="47" spans="1:3" ht="24" customHeight="1">
       <c r="A47" t="s">
         <v>361</v>
       </c>
@@ -8806,8 +10587,9 @@
       <c r="C47" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="F47" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="48" spans="1:3" ht="24" customHeight="1">
       <c r="A48" t="s">
         <v>385</v>
       </c>
@@ -8817,8 +10599,9 @@
       <c r="C48" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="F48" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="49" spans="1:3" ht="24" customHeight="1">
       <c r="A49" t="s">
         <v>273</v>
       </c>
@@ -8828,8 +10611,9 @@
       <c r="C49" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
+      <c r="F49" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="50" spans="1:3" ht="24" customHeight="1">
       <c r="A50" t="s">
         <v>303</v>
       </c>
@@ -8839,8 +10623,9 @@
       <c r="C50" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
+      <c r="F50" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="51" spans="1:3" ht="24" customHeight="1">
       <c r="A51" t="s">
         <v>313</v>
       </c>
@@ -8850,8 +10635,9 @@
       <c r="C51" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="F51" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="52" spans="1:3" ht="24" customHeight="1">
       <c r="A52" t="s">
         <v>343</v>
       </c>
@@ -8861,8 +10647,9 @@
       <c r="C52" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="F52" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="53" spans="1:3" ht="24" customHeight="1">
       <c r="A53" t="s">
         <v>347</v>
       </c>
@@ -8872,8 +10659,9 @@
       <c r="C53" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
+      <c r="F53" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="54" spans="1:3" ht="24" customHeight="1">
       <c r="A54" t="s">
         <v>347</v>
       </c>
@@ -8883,8 +10671,9 @@
       <c r="C54" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="F54" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="55" spans="1:3" ht="24" customHeight="1">
       <c r="A55" t="s">
         <v>352</v>
       </c>
@@ -8894,8 +10683,9 @@
       <c r="C55" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="F55" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="56" spans="1:3" ht="24" customHeight="1">
       <c r="A56" t="s">
         <v>405</v>
       </c>
@@ -8905,8 +10695,9 @@
       <c r="C56" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="F56" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="57" spans="1:3" ht="24" customHeight="1">
       <c r="A57" t="s">
         <v>415</v>
       </c>
@@ -8916,8 +10707,9 @@
       <c r="C57" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="F57" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="58" spans="1:3" ht="24" customHeight="1">
       <c r="A58" t="s">
         <v>415</v>
       </c>
@@ -8927,8 +10719,9 @@
       <c r="C58" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="F58" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="59" spans="1:3" ht="24" customHeight="1">
       <c r="A59" t="s">
         <v>433</v>
       </c>
@@ -8938,8 +10731,9 @@
       <c r="C59" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
+      <c r="F59" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="60" spans="1:3" ht="24" customHeight="1">
       <c r="A60" t="s">
         <v>433</v>
       </c>
@@ -8949,8 +10743,9 @@
       <c r="C60" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="F60" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="61" spans="1:3" ht="24" customHeight="1">
       <c r="A61" t="s">
         <v>433</v>
       </c>
@@ -8960,8 +10755,9 @@
       <c r="C61" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="F61" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="62" spans="1:3" ht="24" customHeight="1">
       <c r="A62" t="s">
         <v>328</v>
       </c>
@@ -8971,8 +10767,9 @@
       <c r="C62" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="F62" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="63" spans="1:3" ht="24" customHeight="1">
       <c r="A63" t="s">
         <v>328</v>
       </c>
@@ -8982,8 +10779,9 @@
       <c r="C63" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="F63" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="64" spans="1:3" ht="24" customHeight="1">
       <c r="A64" t="s">
         <v>283</v>
       </c>
@@ -8993,8 +10791,9 @@
       <c r="C64" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
+      <c r="F64" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="65" spans="1:3" ht="24" customHeight="1">
       <c r="A65" t="s">
         <v>438</v>
       </c>
@@ -9004,8 +10803,9 @@
       <c r="C65" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="F65" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="66" spans="1:3" ht="24" customHeight="1">
       <c r="A66" t="s">
         <v>380</v>
       </c>
@@ -9015,8 +10815,9 @@
       <c r="C66" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="F66" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="67" spans="1:3" ht="24" customHeight="1">
       <c r="A67" t="s">
         <v>293</v>
       </c>
@@ -9026,8 +10827,9 @@
       <c r="C67" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="F67" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="68" spans="1:3" ht="24" customHeight="1">
       <c r="A68" t="s">
         <v>293</v>
       </c>
@@ -9037,8 +10839,9 @@
       <c r="C68" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
+      <c r="F68" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="69" spans="1:3" ht="24" customHeight="1">
       <c r="A69" t="s">
         <v>539</v>
       </c>
@@ -9048,8 +10851,9 @@
       <c r="C69" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="F69" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="70" spans="1:3" ht="24" customHeight="1">
       <c r="A70" t="s">
         <v>530</v>
       </c>
@@ -9059,8 +10863,9 @@
       <c r="C70" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="F70" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="71" spans="1:3" ht="24" customHeight="1">
       <c r="A71" t="s">
         <v>539</v>
       </c>
@@ -9070,8 +10875,9 @@
       <c r="C71" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="F71" s="5" t="str"/>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="72" spans="1:3" ht="24" customHeight="1">
       <c r="A72" t="s">
         <v>539</v>
       </c>
@@ -9081,6 +10887,7 @@
       <c r="C72" t="s">
         <v>628</v>
       </c>
+      <c r="F72" s="5" t="str"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
